--- a/data/nzd0086/nzd0086.xlsx
+++ b/data/nzd0086/nzd0086.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W286"/>
+  <dimension ref="A1:W287"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21667,7 +21667,7 @@
         <v>231.87</v>
       </c>
       <c r="D286" t="n">
-        <v>212.4</v>
+        <v>217.52</v>
       </c>
       <c r="E286" t="n">
         <v>246.53</v>
@@ -21726,6 +21726,81 @@
       <c r="W286" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:12:09+00:00</t>
+        </is>
+      </c>
+      <c r="B287" t="n">
+        <v>303.72</v>
+      </c>
+      <c r="C287" t="n">
+        <v>232.56</v>
+      </c>
+      <c r="D287" t="n">
+        <v>213.53</v>
+      </c>
+      <c r="E287" t="n">
+        <v>246.75</v>
+      </c>
+      <c r="F287" t="n">
+        <v>256.77</v>
+      </c>
+      <c r="G287" t="n">
+        <v>264.27</v>
+      </c>
+      <c r="H287" t="n">
+        <v>271.48</v>
+      </c>
+      <c r="I287" t="n">
+        <v>272.4</v>
+      </c>
+      <c r="J287" t="n">
+        <v>269.81</v>
+      </c>
+      <c r="K287" t="n">
+        <v>271.48</v>
+      </c>
+      <c r="L287" t="n">
+        <v>274.57</v>
+      </c>
+      <c r="M287" t="n">
+        <v>273.1</v>
+      </c>
+      <c r="N287" t="n">
+        <v>265.48</v>
+      </c>
+      <c r="O287" t="n">
+        <v>262.95</v>
+      </c>
+      <c r="P287" t="n">
+        <v>260.18</v>
+      </c>
+      <c r="Q287" t="n">
+        <v>253.34</v>
+      </c>
+      <c r="R287" t="n">
+        <v>251.84</v>
+      </c>
+      <c r="S287" t="n">
+        <v>258.13</v>
+      </c>
+      <c r="T287" t="n">
+        <v>258.26</v>
+      </c>
+      <c r="U287" t="n">
+        <v>266.99</v>
+      </c>
+      <c r="V287" t="n">
+        <v>277.92</v>
+      </c>
+      <c r="W287" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -21740,7 +21815,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B290"/>
+  <dimension ref="A1:B291"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24643,6 +24718,16 @@
       </c>
       <c r="B290" t="n">
         <v>-0.38</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B291" t="n">
+        <v>1.14</v>
       </c>
     </row>
   </sheetData>
@@ -24811,28 +24896,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6674956500969315</v>
+        <v>0.664706436611736</v>
       </c>
       <c r="J2" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="K2" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06472583813534616</v>
+        <v>0.06480963148237451</v>
       </c>
       <c r="M2" t="n">
-        <v>13.97048131610763</v>
+        <v>13.92405754083554</v>
       </c>
       <c r="N2" t="n">
-        <v>309.3415837907122</v>
+        <v>308.0686710562114</v>
       </c>
       <c r="O2" t="n">
-        <v>17.58810915905153</v>
+        <v>17.55188511403295</v>
       </c>
       <c r="P2" t="n">
-        <v>289.2446442524704</v>
+        <v>289.2754828574985</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -24889,28 +24974,28 @@
         <v>0.0101</v>
       </c>
       <c r="I3" t="n">
-        <v>1.28559866878372</v>
+        <v>1.316627640360033</v>
       </c>
       <c r="J3" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="K3" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05777553696113835</v>
+        <v>0.06075003144292135</v>
       </c>
       <c r="M3" t="n">
-        <v>29.43440146964687</v>
+        <v>29.4124054710468</v>
       </c>
       <c r="N3" t="n">
-        <v>1238.022394842089</v>
+        <v>1237.848494937861</v>
       </c>
       <c r="O3" t="n">
-        <v>35.18554241221938</v>
+        <v>35.18307114135805</v>
       </c>
       <c r="P3" t="n">
-        <v>164.1061480073881</v>
+        <v>163.7557299433155</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -24967,28 +25052,28 @@
         <v>0.0205</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.096262990137439</v>
+        <v>-1.096321467785626</v>
       </c>
       <c r="J4" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="K4" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L4" t="n">
-        <v>0.07257732462882416</v>
+        <v>0.07314719145199045</v>
       </c>
       <c r="M4" t="n">
-        <v>19.49401004692471</v>
+        <v>19.42247867729962</v>
       </c>
       <c r="N4" t="n">
-        <v>715.8909868531657</v>
+        <v>713.2139443268014</v>
       </c>
       <c r="O4" t="n">
-        <v>26.75613923669044</v>
+        <v>26.70606568416249</v>
       </c>
       <c r="P4" t="n">
-        <v>247.4055184985463</v>
+        <v>247.4063056524034</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -25045,28 +25130,28 @@
         <v>0.0258</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4275011812123003</v>
+        <v>-0.4264306314580217</v>
       </c>
       <c r="J5" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="K5" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06750845106319847</v>
+        <v>0.06768512293325124</v>
       </c>
       <c r="M5" t="n">
-        <v>8.602237432524696</v>
+        <v>8.577334970404452</v>
       </c>
       <c r="N5" t="n">
-        <v>132.1556590789625</v>
+        <v>131.7011978354174</v>
       </c>
       <c r="O5" t="n">
-        <v>11.49589748905941</v>
+        <v>11.47611423067135</v>
       </c>
       <c r="P5" t="n">
-        <v>256.4622313299292</v>
+        <v>256.4509864068726</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -25123,28 +25208,28 @@
         <v>0.0318</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4303613555991007</v>
+        <v>-0.4302782405360643</v>
       </c>
       <c r="J6" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="K6" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08968935264854661</v>
+        <v>0.09030266614739935</v>
       </c>
       <c r="M6" t="n">
-        <v>7.690580258390613</v>
+        <v>7.664077094977475</v>
       </c>
       <c r="N6" t="n">
-        <v>98.41009079224452</v>
+        <v>98.06604550507593</v>
       </c>
       <c r="O6" t="n">
-        <v>9.920186026090667</v>
+        <v>9.90283017652408</v>
       </c>
       <c r="P6" t="n">
-        <v>267.930029898739</v>
+        <v>267.9291568683311</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -25201,28 +25286,28 @@
         <v>0.039</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3825041737781094</v>
+        <v>-0.3864378968033196</v>
       </c>
       <c r="J7" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="K7" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L7" t="n">
-        <v>0.08927564586539039</v>
+        <v>0.09149688280199075</v>
       </c>
       <c r="M7" t="n">
-        <v>7.146471027763565</v>
+        <v>7.136878786163313</v>
       </c>
       <c r="N7" t="n">
-        <v>78.13590960138166</v>
+        <v>77.96561134061598</v>
       </c>
       <c r="O7" t="n">
-        <v>8.839451883537896</v>
+        <v>8.829813777233129</v>
       </c>
       <c r="P7" t="n">
-        <v>279.7459360222755</v>
+        <v>279.7872553655077</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -25279,28 +25364,28 @@
         <v>0.0536</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3167716178596456</v>
+        <v>-0.3218531251431889</v>
       </c>
       <c r="J8" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="K8" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L8" t="n">
-        <v>0.06146809492482119</v>
+        <v>0.06367083058491974</v>
       </c>
       <c r="M8" t="n">
-        <v>7.416270128474626</v>
+        <v>7.414896997946951</v>
       </c>
       <c r="N8" t="n">
-        <v>80.20772140847555</v>
+        <v>80.09899081921897</v>
       </c>
       <c r="O8" t="n">
-        <v>8.955876361835035</v>
+        <v>8.949803954233801</v>
       </c>
       <c r="P8" t="n">
-        <v>286.8231054629026</v>
+        <v>286.8764809909304</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -25357,28 +25442,28 @@
         <v>0.0876</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2002430535548849</v>
+        <v>-0.2030861361228326</v>
       </c>
       <c r="J9" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="K9" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02832825115367199</v>
+        <v>0.02931692331903113</v>
       </c>
       <c r="M9" t="n">
-        <v>6.927025169743358</v>
+        <v>6.917177354356339</v>
       </c>
       <c r="N9" t="n">
-        <v>72.00109415180604</v>
+        <v>71.80309530560558</v>
       </c>
       <c r="O9" t="n">
-        <v>8.485345847507103</v>
+        <v>8.473670710241553</v>
       </c>
       <c r="P9" t="n">
-        <v>281.5850341784546</v>
+        <v>281.6148975683552</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -25435,28 +25520,28 @@
         <v>0.0806</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1150378130251348</v>
+        <v>-0.1207638620856898</v>
       </c>
       <c r="J10" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="K10" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01182196402658597</v>
+        <v>0.01306526252673024</v>
       </c>
       <c r="M10" t="n">
-        <v>6.204414271300549</v>
+        <v>6.209559789044155</v>
       </c>
       <c r="N10" t="n">
-        <v>57.90967966106037</v>
+        <v>57.92523805631257</v>
       </c>
       <c r="O10" t="n">
-        <v>7.609840974755016</v>
+        <v>7.610863161055556</v>
       </c>
       <c r="P10" t="n">
-        <v>280.7703521467088</v>
+        <v>280.8304978623531</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -25513,28 +25598,28 @@
         <v>0.06370000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>0.05060096761497378</v>
+        <v>0.04277174983078342</v>
       </c>
       <c r="J11" t="n">
+        <v>286</v>
+      </c>
+      <c r="K11" t="n">
         <v>285</v>
       </c>
-      <c r="K11" t="n">
-        <v>284</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.002487340804116833</v>
+        <v>0.001778939808321556</v>
       </c>
       <c r="M11" t="n">
-        <v>5.855741361236566</v>
+        <v>5.869260738515629</v>
       </c>
       <c r="N11" t="n">
-        <v>53.73259805662317</v>
+        <v>53.95192291456044</v>
       </c>
       <c r="O11" t="n">
-        <v>7.330252250545214</v>
+        <v>7.345197268593979</v>
       </c>
       <c r="P11" t="n">
-        <v>281.0012287487193</v>
+        <v>281.0835996057726</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -25591,28 +25676,28 @@
         <v>0.0562</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.04045005806809068</v>
+        <v>-0.04820001425693117</v>
       </c>
       <c r="J12" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="K12" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L12" t="n">
-        <v>0.001996292786307974</v>
+        <v>0.002828084810552745</v>
       </c>
       <c r="M12" t="n">
-        <v>5.301829711073165</v>
+        <v>5.324987076831666</v>
       </c>
       <c r="N12" t="n">
-        <v>42.82235837376817</v>
+        <v>43.07204462269429</v>
       </c>
       <c r="O12" t="n">
-        <v>6.543879458988236</v>
+        <v>6.56292957624065</v>
       </c>
       <c r="P12" t="n">
-        <v>286.3774537981164</v>
+        <v>286.4588583855133</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -25669,28 +25754,28 @@
         <v>0.0536</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0280122444614343</v>
+        <v>0.02299788547762082</v>
       </c>
       <c r="J13" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="K13" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0008895960094257305</v>
+        <v>0.0006023395559496825</v>
       </c>
       <c r="M13" t="n">
-        <v>5.40108719318909</v>
+        <v>5.405030699267903</v>
       </c>
       <c r="N13" t="n">
-        <v>46.13609542314242</v>
+        <v>46.14198818221215</v>
       </c>
       <c r="O13" t="n">
-        <v>6.792355660825073</v>
+        <v>6.792789425722848</v>
       </c>
       <c r="P13" t="n">
-        <v>279.3176226521223</v>
+        <v>279.3702928626618</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -25747,28 +25832,28 @@
         <v>0.0689</v>
       </c>
       <c r="I14" t="n">
-        <v>0.02825042528466709</v>
+        <v>0.02319219723600304</v>
       </c>
       <c r="J14" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="K14" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0009741581455268156</v>
+        <v>0.0006593154874742213</v>
       </c>
       <c r="M14" t="n">
-        <v>4.989600674012672</v>
+        <v>4.998061762909776</v>
       </c>
       <c r="N14" t="n">
-        <v>42.84711666685283</v>
+        <v>42.86744784718648</v>
       </c>
       <c r="O14" t="n">
-        <v>6.54577089935577</v>
+        <v>6.547323716388742</v>
       </c>
       <c r="P14" t="n">
-        <v>271.7600061137916</v>
+        <v>271.8131371195971</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -25825,28 +25910,28 @@
         <v>0.0704</v>
       </c>
       <c r="I15" t="n">
-        <v>0.05993521503594851</v>
+        <v>0.0568481872160443</v>
       </c>
       <c r="J15" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="K15" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L15" t="n">
-        <v>0.004432737551042343</v>
+        <v>0.004015043175649269</v>
       </c>
       <c r="M15" t="n">
-        <v>5.037282112814273</v>
+        <v>5.033790540202094</v>
       </c>
       <c r="N15" t="n">
-        <v>42.23641902005051</v>
+        <v>42.15211259092032</v>
       </c>
       <c r="O15" t="n">
-        <v>6.498955225268944</v>
+        <v>6.49246583286507</v>
       </c>
       <c r="P15" t="n">
-        <v>265.6582286965381</v>
+        <v>265.6906544573861</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -25903,28 +25988,28 @@
         <v>0.059</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1127247497619725</v>
+        <v>0.110908126528629</v>
       </c>
       <c r="J16" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="K16" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L16" t="n">
-        <v>0.02156287234356147</v>
+        <v>0.02103453156674773</v>
       </c>
       <c r="M16" t="n">
-        <v>4.289736721638366</v>
+        <v>4.283869206270464</v>
       </c>
       <c r="N16" t="n">
-        <v>30.18486499744406</v>
+        <v>30.10126951065633</v>
       </c>
       <c r="O16" t="n">
-        <v>5.494075445190397</v>
+        <v>5.486462385787068</v>
       </c>
       <c r="P16" t="n">
-        <v>259.7422446638753</v>
+        <v>259.7613262510692</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -25981,28 +26066,28 @@
         <v>0.0731</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1316865263921709</v>
+        <v>0.1283934935898725</v>
       </c>
       <c r="J17" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="K17" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L17" t="n">
-        <v>0.03272906459950553</v>
+        <v>0.03131985487315347</v>
       </c>
       <c r="M17" t="n">
-        <v>4.164569560163326</v>
+        <v>4.164929725533517</v>
       </c>
       <c r="N17" t="n">
-        <v>26.83005697321715</v>
+        <v>26.80835927950076</v>
       </c>
       <c r="O17" t="n">
-        <v>5.179773834176271</v>
+        <v>5.177678947124933</v>
       </c>
       <c r="P17" t="n">
-        <v>254.4621490252529</v>
+        <v>254.4967386371196</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -26059,28 +26144,28 @@
         <v>0.08309999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1272186200194802</v>
+        <v>0.1238308365785664</v>
       </c>
       <c r="J18" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="K18" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L18" t="n">
-        <v>0.03233172224288172</v>
+        <v>0.03082970018648867</v>
       </c>
       <c r="M18" t="n">
-        <v>3.975188891522339</v>
+        <v>3.978773829881956</v>
       </c>
       <c r="N18" t="n">
-        <v>25.35849011921393</v>
+        <v>25.34614732995684</v>
       </c>
       <c r="O18" t="n">
-        <v>5.035721410008096</v>
+        <v>5.034495737405767</v>
       </c>
       <c r="P18" t="n">
-        <v>253.2061609177683</v>
+        <v>253.2417457786988</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -26137,28 +26222,28 @@
         <v>0.0756</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1211210787378164</v>
+        <v>0.1183196102897632</v>
       </c>
       <c r="J19" t="n">
+        <v>286</v>
+      </c>
+      <c r="K19" t="n">
         <v>285</v>
       </c>
-      <c r="K19" t="n">
-        <v>284</v>
-      </c>
       <c r="L19" t="n">
-        <v>0.02262738248993112</v>
+        <v>0.02174853103960617</v>
       </c>
       <c r="M19" t="n">
-        <v>4.542859626462052</v>
+        <v>4.542031834409325</v>
       </c>
       <c r="N19" t="n">
-        <v>33.28274071111005</v>
+        <v>33.21837213227636</v>
       </c>
       <c r="O19" t="n">
-        <v>5.769119578506763</v>
+        <v>5.763538160910914</v>
       </c>
       <c r="P19" t="n">
-        <v>258.8430221248005</v>
+        <v>258.8724139681656</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -26215,28 +26300,28 @@
         <v>0.0958</v>
       </c>
       <c r="I20" t="n">
-        <v>0.03861086244513687</v>
+        <v>0.03696614683024867</v>
       </c>
       <c r="J20" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="K20" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L20" t="n">
-        <v>0.002961467729402645</v>
+        <v>0.002734747233841706</v>
       </c>
       <c r="M20" t="n">
-        <v>4.029136313785466</v>
+        <v>4.023039478172453</v>
       </c>
       <c r="N20" t="n">
-        <v>26.2753378501581</v>
+        <v>26.20145504945108</v>
       </c>
       <c r="O20" t="n">
-        <v>5.125947507550004</v>
+        <v>5.118735688571064</v>
       </c>
       <c r="P20" t="n">
-        <v>259.5330613243212</v>
+        <v>259.550337215017</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -26293,28 +26378,28 @@
         <v>0.06610000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1913697070947964</v>
+        <v>0.1872235821655353</v>
       </c>
       <c r="J21" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="K21" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0708475320284635</v>
+        <v>0.06822842205954749</v>
       </c>
       <c r="M21" t="n">
-        <v>3.755489959095431</v>
+        <v>3.765795136859236</v>
       </c>
       <c r="N21" t="n">
-        <v>25.14392129956843</v>
+        <v>25.17032238027199</v>
       </c>
       <c r="O21" t="n">
-        <v>5.014371476024531</v>
+        <v>5.01700332671526</v>
       </c>
       <c r="P21" t="n">
-        <v>267.7308037558309</v>
+        <v>267.7743541425606</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -26371,28 +26456,28 @@
         <v>0.06279999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2891752098943778</v>
+        <v>0.2863136575709764</v>
       </c>
       <c r="J22" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="K22" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L22" t="n">
-        <v>0.09284138507172746</v>
+        <v>0.09172805538092899</v>
       </c>
       <c r="M22" t="n">
-        <v>5.154855424666615</v>
+        <v>5.153504156694956</v>
       </c>
       <c r="N22" t="n">
-        <v>42.77481137214452</v>
+        <v>42.67970299765898</v>
       </c>
       <c r="O22" t="n">
-        <v>6.540245513139741</v>
+        <v>6.532970457430446</v>
       </c>
       <c r="P22" t="n">
-        <v>274.3103862405862</v>
+        <v>274.3404436345283</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -26430,7 +26515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W286"/>
+  <dimension ref="A1:W287"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59408,7 +59493,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>-35.513942770558366,174.4682909125168</t>
+          <t>-35.513983812782115,174.4683167379183</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
@@ -59504,6 +59589,123 @@
       <c r="W286" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:12:09+00:00</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>-35.51424445461009,174.47059770739537</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>-35.51382565701153,174.46951351183793</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>-35.51395182870594,174.4682966122613</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>-35.51479757936153,174.46751127231494</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>-35.51539313028691,174.46688796211598</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>-35.51597322683597,174.46624806642643</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>-35.516662055213956,174.46562340844253</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>-35.517374479447845,174.46513857987733</t>
+        </is>
+      </c>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>-35.51800110844648,174.46467434913873</t>
+        </is>
+      </c>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>-35.518646161410835,174.4642513281102</t>
+        </is>
+      </c>
+      <c r="L287" t="inlineStr">
+        <is>
+          <t>-35.51934540236641,174.46381157358772</t>
+        </is>
+      </c>
+      <c r="M287" t="inlineStr">
+        <is>
+          <t>-35.520074123798494,174.46344001582972</t>
+        </is>
+      </c>
+      <c r="N287" t="inlineStr">
+        <is>
+          <t>-35.52073709538975,174.46303922239045</t>
+        </is>
+      </c>
+      <c r="O287" t="inlineStr">
+        <is>
+          <t>-35.52142362982122,174.4626876305622</t>
+        </is>
+      </c>
+      <c r="P287" t="inlineStr">
+        <is>
+          <t>-35.52212859294319,174.46235132454353</t>
+        </is>
+      </c>
+      <c r="Q287" t="inlineStr">
+        <is>
+          <t>-35.52281862098883,174.46200029412498</t>
+        </is>
+      </c>
+      <c r="R287" t="inlineStr">
+        <is>
+          <t>-35.52351416253607,174.4617090367058</t>
+        </is>
+      </c>
+      <c r="S287" t="inlineStr">
+        <is>
+          <t>-35.52431641723523,174.46147900207237</t>
+        </is>
+      </c>
+      <c r="T287" t="inlineStr">
+        <is>
+          <t>-35.525129630032396,174.46135918826798</t>
+        </is>
+      </c>
+      <c r="U287" t="inlineStr">
+        <is>
+          <t>-35.52586442207795,174.4613507849518</t>
+        </is>
+      </c>
+      <c r="V287" t="inlineStr">
+        <is>
+          <t>-35.52660130461187,174.46136706107012</t>
+        </is>
+      </c>
+      <c r="W287" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>

--- a/data/nzd0086/nzd0086.xlsx
+++ b/data/nzd0086/nzd0086.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W287"/>
+  <dimension ref="A1:W288"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21799,6 +21799,81 @@
         <v>277.92</v>
       </c>
       <c r="W287" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:12:06+00:00</t>
+        </is>
+      </c>
+      <c r="B288" t="n">
+        <v>303.72</v>
+      </c>
+      <c r="C288" t="n">
+        <v>243.46</v>
+      </c>
+      <c r="D288" t="n">
+        <v>207.32</v>
+      </c>
+      <c r="E288" t="n">
+        <v>245.26</v>
+      </c>
+      <c r="F288" t="n">
+        <v>255.02</v>
+      </c>
+      <c r="G288" t="n">
+        <v>265.3</v>
+      </c>
+      <c r="H288" t="n">
+        <v>271.77</v>
+      </c>
+      <c r="I288" t="n">
+        <v>270.49</v>
+      </c>
+      <c r="J288" t="n">
+        <v>267.32</v>
+      </c>
+      <c r="K288" t="n">
+        <v>269.92</v>
+      </c>
+      <c r="L288" t="n">
+        <v>275.51</v>
+      </c>
+      <c r="M288" t="n">
+        <v>276.06</v>
+      </c>
+      <c r="N288" t="n">
+        <v>266.1</v>
+      </c>
+      <c r="O288" t="n">
+        <v>264.06</v>
+      </c>
+      <c r="P288" t="n">
+        <v>260.24</v>
+      </c>
+      <c r="Q288" t="n">
+        <v>254.06</v>
+      </c>
+      <c r="R288" t="n">
+        <v>252.07</v>
+      </c>
+      <c r="S288" t="n">
+        <v>260.32</v>
+      </c>
+      <c r="T288" t="n">
+        <v>259.15</v>
+      </c>
+      <c r="U288" t="n">
+        <v>266.95</v>
+      </c>
+      <c r="V288" t="n">
+        <v>279.64</v>
+      </c>
+      <c r="W288" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -21815,7 +21890,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B291"/>
+  <dimension ref="A1:B292"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24728,6 +24803,16 @@
       </c>
       <c r="B291" t="n">
         <v>1.14</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B292" t="n">
+        <v>0.72</v>
       </c>
     </row>
   </sheetData>
@@ -24896,28 +24981,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.664706436611736</v>
+        <v>0.661918700538231</v>
       </c>
       <c r="J2" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K2" t="n">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06480963148237451</v>
+        <v>0.06489048347164428</v>
       </c>
       <c r="M2" t="n">
-        <v>13.92405754083554</v>
+        <v>13.87790732149236</v>
       </c>
       <c r="N2" t="n">
-        <v>308.0686710562114</v>
+        <v>306.8069035995054</v>
       </c>
       <c r="O2" t="n">
-        <v>17.55188511403295</v>
+        <v>17.51590430436023</v>
       </c>
       <c r="P2" t="n">
-        <v>289.2754828574985</v>
+        <v>289.306409961304</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -24974,28 +25059,28 @@
         <v>0.0101</v>
       </c>
       <c r="I3" t="n">
-        <v>1.316627640360033</v>
+        <v>1.35665772575506</v>
       </c>
       <c r="J3" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K3" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06075003144292135</v>
+        <v>0.06444649839555472</v>
       </c>
       <c r="M3" t="n">
-        <v>29.4124054710468</v>
+        <v>29.42061767599201</v>
       </c>
       <c r="N3" t="n">
-        <v>1237.848494937861</v>
+        <v>1240.852645920103</v>
       </c>
       <c r="O3" t="n">
-        <v>35.18307114135805</v>
+        <v>35.22573840134658</v>
       </c>
       <c r="P3" t="n">
-        <v>163.7557299433155</v>
+        <v>163.3022048299125</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -25052,28 +25137,28 @@
         <v>0.0205</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.096321467785626</v>
+        <v>-1.105333584349643</v>
       </c>
       <c r="J4" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K4" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L4" t="n">
-        <v>0.07314719145199045</v>
+        <v>0.07479139465545337</v>
       </c>
       <c r="M4" t="n">
-        <v>19.42247867729962</v>
+        <v>19.393252522034</v>
       </c>
       <c r="N4" t="n">
-        <v>713.2139443268014</v>
+        <v>711.0611311191407</v>
       </c>
       <c r="O4" t="n">
-        <v>26.70606568416249</v>
+        <v>26.66572952535034</v>
       </c>
       <c r="P4" t="n">
-        <v>247.4063056524034</v>
+        <v>247.5093303914895</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -25130,28 +25215,28 @@
         <v>0.0258</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4264306314580217</v>
+        <v>-0.4264183817309608</v>
       </c>
       <c r="J5" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K5" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06768512293325124</v>
+        <v>0.06818076367412096</v>
       </c>
       <c r="M5" t="n">
-        <v>8.577334970404452</v>
+        <v>8.547507379479782</v>
       </c>
       <c r="N5" t="n">
-        <v>131.7011978354174</v>
+        <v>131.2423096453994</v>
       </c>
       <c r="O5" t="n">
-        <v>11.47611423067135</v>
+        <v>11.45610359788176</v>
       </c>
       <c r="P5" t="n">
-        <v>256.4509864068726</v>
+        <v>256.4508572610679</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -25208,28 +25293,28 @@
         <v>0.0318</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4302782405360643</v>
+        <v>-0.4314268024225672</v>
       </c>
       <c r="J6" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K6" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="L6" t="n">
-        <v>0.09030266614739935</v>
+        <v>0.09138682427409162</v>
       </c>
       <c r="M6" t="n">
-        <v>7.664077094977475</v>
+        <v>7.643095096952123</v>
       </c>
       <c r="N6" t="n">
-        <v>98.06604550507593</v>
+        <v>97.73315252232702</v>
       </c>
       <c r="O6" t="n">
-        <v>9.90283017652408</v>
+        <v>9.886007916359718</v>
       </c>
       <c r="P6" t="n">
-        <v>267.9291568683311</v>
+        <v>267.9412658686741</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -25286,28 +25371,28 @@
         <v>0.039</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3864378968033196</v>
+        <v>-0.3895476518458872</v>
       </c>
       <c r="J7" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K7" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="L7" t="n">
-        <v>0.09149688280199075</v>
+        <v>0.09343403701203901</v>
       </c>
       <c r="M7" t="n">
-        <v>7.136878786163313</v>
+        <v>7.124008446685789</v>
       </c>
       <c r="N7" t="n">
-        <v>77.96561134061598</v>
+        <v>77.75846811086187</v>
       </c>
       <c r="O7" t="n">
-        <v>8.829813777233129</v>
+        <v>8.818076213713617</v>
       </c>
       <c r="P7" t="n">
-        <v>279.7872553655077</v>
+        <v>279.8200407341672</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -25364,28 +25449,28 @@
         <v>0.0536</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3218531251431889</v>
+        <v>-0.3266266602588386</v>
       </c>
       <c r="J8" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K8" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="L8" t="n">
-        <v>0.06367083058491974</v>
+        <v>0.0658158488208973</v>
       </c>
       <c r="M8" t="n">
-        <v>7.414896997946951</v>
+        <v>7.41184929950299</v>
       </c>
       <c r="N8" t="n">
-        <v>80.09899081921897</v>
+        <v>79.97191353992655</v>
       </c>
       <c r="O8" t="n">
-        <v>8.949803954233801</v>
+        <v>8.942701691319384</v>
       </c>
       <c r="P8" t="n">
-        <v>286.8764809909304</v>
+        <v>286.9268071762515</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -25442,28 +25527,28 @@
         <v>0.0876</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2030861361228326</v>
+        <v>-0.207246816037504</v>
       </c>
       <c r="J9" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K9" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02931692331903113</v>
+        <v>0.03067945795732818</v>
       </c>
       <c r="M9" t="n">
-        <v>6.917177354356339</v>
+        <v>6.913859943479652</v>
       </c>
       <c r="N9" t="n">
-        <v>71.80309530560558</v>
+        <v>71.66839645423038</v>
       </c>
       <c r="O9" t="n">
-        <v>8.473670710241553</v>
+        <v>8.465718897661933</v>
       </c>
       <c r="P9" t="n">
-        <v>281.6148975683552</v>
+        <v>281.6587625747654</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -25520,28 +25605,28 @@
         <v>0.0806</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1207638620856898</v>
+        <v>-0.1281947079792226</v>
       </c>
       <c r="J10" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K10" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01306526252673024</v>
+        <v>0.0147203220378036</v>
       </c>
       <c r="M10" t="n">
-        <v>6.209559789044155</v>
+        <v>6.223210015776502</v>
       </c>
       <c r="N10" t="n">
-        <v>57.92523805631257</v>
+        <v>58.09177248322237</v>
       </c>
       <c r="O10" t="n">
-        <v>7.610863161055556</v>
+        <v>7.621795883072596</v>
       </c>
       <c r="P10" t="n">
-        <v>280.8304978623531</v>
+        <v>280.9088394097535</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -25598,28 +25683,28 @@
         <v>0.06370000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>0.04277174983078342</v>
+        <v>0.03393175021963192</v>
       </c>
       <c r="J11" t="n">
+        <v>287</v>
+      </c>
+      <c r="K11" t="n">
         <v>286</v>
       </c>
-      <c r="K11" t="n">
-        <v>285</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.001778939808321556</v>
+        <v>0.001118343100619201</v>
       </c>
       <c r="M11" t="n">
-        <v>5.869260738515629</v>
+        <v>5.887017663448364</v>
       </c>
       <c r="N11" t="n">
-        <v>53.95192291456044</v>
+        <v>54.28487780340835</v>
       </c>
       <c r="O11" t="n">
-        <v>7.345197268593979</v>
+        <v>7.367827210474493</v>
       </c>
       <c r="P11" t="n">
-        <v>281.0835996057726</v>
+        <v>281.1769500406837</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -25676,28 +25761,28 @@
         <v>0.0562</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.04820001425693117</v>
+        <v>-0.05515571865400271</v>
       </c>
       <c r="J12" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K12" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="L12" t="n">
-        <v>0.002828084810552745</v>
+        <v>0.003701430714222465</v>
       </c>
       <c r="M12" t="n">
-        <v>5.324987076831666</v>
+        <v>5.343884506965957</v>
       </c>
       <c r="N12" t="n">
-        <v>43.07204462269429</v>
+        <v>43.24473064883362</v>
       </c>
       <c r="O12" t="n">
-        <v>6.56292957624065</v>
+        <v>6.576072585429211</v>
       </c>
       <c r="P12" t="n">
-        <v>286.4588583855133</v>
+        <v>286.5321906351031</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -25754,28 +25839,28 @@
         <v>0.0536</v>
       </c>
       <c r="I13" t="n">
-        <v>0.02299788547762082</v>
+        <v>0.02018563453647973</v>
       </c>
       <c r="J13" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K13" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0006023395559496825</v>
+        <v>0.0004672352345728159</v>
       </c>
       <c r="M13" t="n">
-        <v>5.405030699267903</v>
+        <v>5.398841281785909</v>
       </c>
       <c r="N13" t="n">
-        <v>46.14198818221215</v>
+        <v>46.03397526842386</v>
       </c>
       <c r="O13" t="n">
-        <v>6.792789425722848</v>
+        <v>6.784834210828136</v>
       </c>
       <c r="P13" t="n">
-        <v>279.3702928626618</v>
+        <v>279.3999417200818</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -25832,28 +25917,28 @@
         <v>0.0689</v>
       </c>
       <c r="I14" t="n">
-        <v>0.02319219723600304</v>
+        <v>0.01864779193771647</v>
       </c>
       <c r="J14" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K14" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0006593154874742213</v>
+        <v>0.000428342164437101</v>
       </c>
       <c r="M14" t="n">
-        <v>4.998061762909776</v>
+        <v>5.003649320462851</v>
       </c>
       <c r="N14" t="n">
-        <v>42.86744784718648</v>
+        <v>42.85585415408491</v>
       </c>
       <c r="O14" t="n">
-        <v>6.547323716388742</v>
+        <v>6.54643828001799</v>
       </c>
       <c r="P14" t="n">
-        <v>271.8131371195971</v>
+        <v>271.8610476466331</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -25910,28 +25995,28 @@
         <v>0.0704</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0568481872160443</v>
+        <v>0.05460358736757498</v>
       </c>
       <c r="J15" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K15" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="L15" t="n">
-        <v>0.004015043175649269</v>
+        <v>0.003731642758367459</v>
       </c>
       <c r="M15" t="n">
-        <v>5.033790540202094</v>
+        <v>5.026392525941778</v>
       </c>
       <c r="N15" t="n">
-        <v>42.15211259092032</v>
+        <v>42.03885194157083</v>
       </c>
       <c r="O15" t="n">
-        <v>6.49246583286507</v>
+        <v>6.483737497892002</v>
       </c>
       <c r="P15" t="n">
-        <v>265.6906544573861</v>
+        <v>265.714318711489</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -25988,28 +26073,28 @@
         <v>0.059</v>
       </c>
       <c r="I16" t="n">
-        <v>0.110908126528629</v>
+        <v>0.1091564521617005</v>
       </c>
       <c r="J16" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K16" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="L16" t="n">
-        <v>0.02103453156674773</v>
+        <v>0.02053314973145404</v>
       </c>
       <c r="M16" t="n">
-        <v>4.283869206270464</v>
+        <v>4.277671415982685</v>
       </c>
       <c r="N16" t="n">
-        <v>30.10126951065633</v>
+        <v>30.01685657641596</v>
       </c>
       <c r="O16" t="n">
-        <v>5.486462385787068</v>
+        <v>5.47876414681413</v>
       </c>
       <c r="P16" t="n">
-        <v>259.7613262510692</v>
+        <v>259.7797937152601</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -26066,28 +26151,28 @@
         <v>0.0731</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1283934935898725</v>
+        <v>0.1256582427685796</v>
       </c>
       <c r="J17" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K17" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="L17" t="n">
-        <v>0.03131985487315347</v>
+        <v>0.03021513832811518</v>
       </c>
       <c r="M17" t="n">
-        <v>4.164929725533517</v>
+        <v>4.162878323297392</v>
       </c>
       <c r="N17" t="n">
-        <v>26.80835927950076</v>
+        <v>26.76486128542264</v>
       </c>
       <c r="O17" t="n">
-        <v>5.177678947124933</v>
+        <v>5.17347671159566</v>
       </c>
       <c r="P17" t="n">
-        <v>254.4967386371196</v>
+        <v>254.5255757015586</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -26144,28 +26229,28 @@
         <v>0.08309999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1238308365785664</v>
+        <v>0.1206463985403926</v>
       </c>
       <c r="J18" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K18" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="L18" t="n">
-        <v>0.03082970018648867</v>
+        <v>0.02945894016636563</v>
       </c>
       <c r="M18" t="n">
-        <v>3.978773829881956</v>
+        <v>3.981153416316</v>
       </c>
       <c r="N18" t="n">
-        <v>25.34614732995684</v>
+        <v>25.32548308669848</v>
       </c>
       <c r="O18" t="n">
-        <v>5.034495737405767</v>
+        <v>5.032443053497822</v>
       </c>
       <c r="P18" t="n">
-        <v>253.2417457786988</v>
+        <v>253.2753185114786</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -26222,28 +26307,28 @@
         <v>0.0756</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1183196102897632</v>
+        <v>0.1171273523988806</v>
       </c>
       <c r="J19" t="n">
+        <v>287</v>
+      </c>
+      <c r="K19" t="n">
         <v>286</v>
       </c>
-      <c r="K19" t="n">
-        <v>285</v>
-      </c>
       <c r="L19" t="n">
-        <v>0.02174853103960617</v>
+        <v>0.02148069335790137</v>
       </c>
       <c r="M19" t="n">
-        <v>4.542031834409325</v>
+        <v>4.53250974888441</v>
       </c>
       <c r="N19" t="n">
-        <v>33.21837213227636</v>
+        <v>33.11174706753823</v>
       </c>
       <c r="O19" t="n">
-        <v>5.763538160910914</v>
+        <v>5.754280760228704</v>
       </c>
       <c r="P19" t="n">
-        <v>258.8724139681656</v>
+        <v>258.8849691964667</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -26300,28 +26385,28 @@
         <v>0.0958</v>
       </c>
       <c r="I20" t="n">
-        <v>0.03696614683024867</v>
+        <v>0.03598296896702607</v>
       </c>
       <c r="J20" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K20" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="L20" t="n">
-        <v>0.002734747233841706</v>
+        <v>0.002611402484045011</v>
       </c>
       <c r="M20" t="n">
-        <v>4.023039478172453</v>
+        <v>4.013743547614528</v>
       </c>
       <c r="N20" t="n">
-        <v>26.20145504945108</v>
+        <v>26.11660938148756</v>
       </c>
       <c r="O20" t="n">
-        <v>5.118735688571064</v>
+        <v>5.110441212017565</v>
       </c>
       <c r="P20" t="n">
-        <v>259.550337215017</v>
+        <v>259.5607026130185</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -26378,28 +26463,28 @@
         <v>0.06610000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1872235821655353</v>
+        <v>0.1830959556140564</v>
       </c>
       <c r="J21" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K21" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="L21" t="n">
-        <v>0.06822842205954749</v>
+        <v>0.0656539781041291</v>
       </c>
       <c r="M21" t="n">
-        <v>3.765795136859236</v>
+        <v>3.775764334739525</v>
       </c>
       <c r="N21" t="n">
-        <v>25.17032238027199</v>
+        <v>25.1962794515335</v>
       </c>
       <c r="O21" t="n">
-        <v>5.01700332671526</v>
+        <v>5.019589570027962</v>
       </c>
       <c r="P21" t="n">
-        <v>267.7743541425606</v>
+        <v>267.8178706756401</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -26456,28 +26541,28 @@
         <v>0.06279999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2863136575709764</v>
+        <v>0.284715142058472</v>
       </c>
       <c r="J22" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K22" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="L22" t="n">
-        <v>0.09172805538092899</v>
+        <v>0.091419186874935</v>
       </c>
       <c r="M22" t="n">
-        <v>5.153504156694956</v>
+        <v>5.144846477946265</v>
       </c>
       <c r="N22" t="n">
-        <v>42.67970299765898</v>
+        <v>42.54803972236287</v>
       </c>
       <c r="O22" t="n">
-        <v>6.532970457430446</v>
+        <v>6.522885843119046</v>
       </c>
       <c r="P22" t="n">
-        <v>274.3404436345283</v>
+        <v>274.3572963832715</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -26515,7 +26600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W287"/>
+  <dimension ref="A1:W288"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59709,6 +59794,123 @@
         </is>
       </c>
     </row>
+    <row r="288">
+      <c r="A288" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:12:06+00:00</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>-35.51424445461009,174.47059770739537</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>-35.513920006343575,174.46954708032627</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>-35.51390204897063,174.4682652889028</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>-35.514787449383846,174.46750048413364</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>-35.51538171019817,174.46687465022518</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>-35.51597960646669,174.46625631804966</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>-35.5166635359958,174.46562604359826</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>-35.517366216698356,174.46512010331728</t>
+        </is>
+      </c>
+      <c r="J288" t="inlineStr">
+        <is>
+          <t>-35.51799033653007,174.46465026174494</t>
+        </is>
+      </c>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>-35.51863941270919,174.4642362371106</t>
+        </is>
+      </c>
+      <c r="L288" t="inlineStr">
+        <is>
+          <t>-35.519348953256525,174.46382098453697</t>
+        </is>
+      </c>
+      <c r="M288" t="inlineStr">
+        <is>
+          <t>-35.52008350620989,174.4634705702309</t>
+        </is>
+      </c>
+      <c r="N288" t="inlineStr">
+        <is>
+          <t>-35.520739034921796,174.46304563407264</t>
+        </is>
+      </c>
+      <c r="O288" t="inlineStr">
+        <is>
+          <t>-35.52142697553506,174.46269916578999</t>
+        </is>
+      </c>
+      <c r="P288" t="inlineStr">
+        <is>
+          <t>-35.52212875988874,174.46235195385</t>
+        </is>
+      </c>
+      <c r="Q288" t="inlineStr">
+        <is>
+          <t>-35.52282053975132,174.46200787866206</t>
+        </is>
+      </c>
+      <c r="R288" t="inlineStr">
+        <is>
+          <t>-35.523514768606496,174.46171146214877</t>
+        </is>
+      </c>
+      <c r="S288" t="inlineStr">
+        <is>
+          <t>-35.52432033418417,174.46150267141223</t>
+        </is>
+      </c>
+      <c r="T288" t="inlineStr">
+        <is>
+          <t>-35.52513048175806,174.46136894705867</t>
+        </is>
+      </c>
+      <c r="U288" t="inlineStr">
+        <is>
+          <t>-35.52586438390793,174.46135034633616</t>
+        </is>
+      </c>
+      <c r="V288" t="inlineStr">
+        <is>
+          <t>-35.52660294119531,174.46138592233032</t>
+        </is>
+      </c>
+      <c r="W288" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0086/nzd0086.xlsx
+++ b/data/nzd0086/nzd0086.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W288"/>
+  <dimension ref="A1:W290"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21874,6 +21874,156 @@
         <v>279.64</v>
       </c>
       <c r="W288" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:11:34+00:00</t>
+        </is>
+      </c>
+      <c r="B289" t="n">
+        <v>303.72</v>
+      </c>
+      <c r="C289" t="n">
+        <v>243.46</v>
+      </c>
+      <c r="D289" t="n">
+        <v>232.44</v>
+      </c>
+      <c r="E289" t="n">
+        <v>255.17</v>
+      </c>
+      <c r="F289" t="n">
+        <v>262.07</v>
+      </c>
+      <c r="G289" t="n">
+        <v>266.62</v>
+      </c>
+      <c r="H289" t="n">
+        <v>272.97</v>
+      </c>
+      <c r="I289" t="n">
+        <v>270.43</v>
+      </c>
+      <c r="J289" t="n">
+        <v>266.53</v>
+      </c>
+      <c r="K289" t="n">
+        <v>269.97</v>
+      </c>
+      <c r="L289" t="n">
+        <v>275.45</v>
+      </c>
+      <c r="M289" t="n">
+        <v>278.84</v>
+      </c>
+      <c r="N289" t="n">
+        <v>265.55</v>
+      </c>
+      <c r="O289" t="n">
+        <v>263.94</v>
+      </c>
+      <c r="P289" t="n">
+        <v>258.71</v>
+      </c>
+      <c r="Q289" t="n">
+        <v>255.93</v>
+      </c>
+      <c r="R289" t="n">
+        <v>251.42</v>
+      </c>
+      <c r="S289" t="n">
+        <v>262.41</v>
+      </c>
+      <c r="T289" t="n">
+        <v>261.35</v>
+      </c>
+      <c r="U289" t="n">
+        <v>269.05</v>
+      </c>
+      <c r="V289" t="n">
+        <v>280.69</v>
+      </c>
+      <c r="W289" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:11:35+00:00</t>
+        </is>
+      </c>
+      <c r="B290" t="n">
+        <v>283.88</v>
+      </c>
+      <c r="C290" t="n">
+        <v>243.46</v>
+      </c>
+      <c r="D290" t="n">
+        <v>232.44</v>
+      </c>
+      <c r="E290" t="n">
+        <v>255.17</v>
+      </c>
+      <c r="F290" t="n">
+        <v>262.07</v>
+      </c>
+      <c r="G290" t="n">
+        <v>265.71</v>
+      </c>
+      <c r="H290" t="n">
+        <v>272.23</v>
+      </c>
+      <c r="I290" t="n">
+        <v>270.74</v>
+      </c>
+      <c r="J290" t="n">
+        <v>268.97</v>
+      </c>
+      <c r="K290" t="n">
+        <v>272.46</v>
+      </c>
+      <c r="L290" t="n">
+        <v>274.45</v>
+      </c>
+      <c r="M290" t="n">
+        <v>282.14</v>
+      </c>
+      <c r="N290" t="n">
+        <v>262.52</v>
+      </c>
+      <c r="O290" t="n">
+        <v>265.14</v>
+      </c>
+      <c r="P290" t="n">
+        <v>260.13</v>
+      </c>
+      <c r="Q290" t="n">
+        <v>258.13</v>
+      </c>
+      <c r="R290" t="n">
+        <v>254.49</v>
+      </c>
+      <c r="S290" t="n">
+        <v>262.54</v>
+      </c>
+      <c r="T290" t="n">
+        <v>261.49</v>
+      </c>
+      <c r="U290" t="n">
+        <v>268.2</v>
+      </c>
+      <c r="V290" t="n">
+        <v>280.12</v>
+      </c>
+      <c r="W290" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -21890,7 +22040,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B292"/>
+  <dimension ref="A1:B294"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24813,6 +24963,26 @@
       </c>
       <c r="B292" t="n">
         <v>0.72</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B293" t="n">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B294" t="n">
+        <v>-0.61</v>
       </c>
     </row>
   </sheetData>
@@ -24981,28 +25151,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.661918700538231</v>
+        <v>0.6379761021027339</v>
       </c>
       <c r="J2" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="K2" t="n">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06489048347164428</v>
+        <v>0.06129141430324059</v>
       </c>
       <c r="M2" t="n">
-        <v>13.87790732149236</v>
+        <v>13.86637196355964</v>
       </c>
       <c r="N2" t="n">
-        <v>306.8069035995054</v>
+        <v>306.452918277079</v>
       </c>
       <c r="O2" t="n">
-        <v>17.51590430436023</v>
+        <v>17.50579670500829</v>
       </c>
       <c r="P2" t="n">
-        <v>289.306409961304</v>
+        <v>289.5746099368026</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -25059,28 +25229,28 @@
         <v>0.0101</v>
       </c>
       <c r="I3" t="n">
-        <v>1.35665772575506</v>
+        <v>1.434675182730626</v>
       </c>
       <c r="J3" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="K3" t="n">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06444649839555472</v>
+        <v>0.07201456017775443</v>
       </c>
       <c r="M3" t="n">
-        <v>29.42061767599201</v>
+        <v>29.42589409123895</v>
       </c>
       <c r="N3" t="n">
-        <v>1240.852645920103</v>
+        <v>1245.966831011822</v>
       </c>
       <c r="O3" t="n">
-        <v>35.22573840134658</v>
+        <v>35.29825535365484</v>
       </c>
       <c r="P3" t="n">
-        <v>163.3022048299125</v>
+        <v>162.4109759234416</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -25137,28 +25307,28 @@
         <v>0.0205</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.105333584349643</v>
+        <v>-1.082610428666785</v>
       </c>
       <c r="J4" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="K4" t="n">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="L4" t="n">
-        <v>0.07479139465545337</v>
+        <v>0.07296617635257363</v>
       </c>
       <c r="M4" t="n">
-        <v>19.393252522034</v>
+        <v>19.35272594371768</v>
       </c>
       <c r="N4" t="n">
-        <v>711.0611311191407</v>
+        <v>707.3286154075776</v>
       </c>
       <c r="O4" t="n">
-        <v>26.66572952535034</v>
+        <v>26.59565030992056</v>
       </c>
       <c r="P4" t="n">
-        <v>247.5093303914895</v>
+        <v>247.2472833980531</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -25215,28 +25385,28 @@
         <v>0.0258</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4264183817309608</v>
+        <v>-0.412044693394206</v>
       </c>
       <c r="J5" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="K5" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06818076367412096</v>
+        <v>0.06460517023334278</v>
       </c>
       <c r="M5" t="n">
-        <v>8.547507379479782</v>
+        <v>8.557890939468056</v>
       </c>
       <c r="N5" t="n">
-        <v>131.2423096453994</v>
+        <v>131.0133860739638</v>
       </c>
       <c r="O5" t="n">
-        <v>11.45610359788176</v>
+        <v>11.44610790067802</v>
       </c>
       <c r="P5" t="n">
-        <v>256.4508572610679</v>
+        <v>256.2978776320865</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -25293,28 +25463,28 @@
         <v>0.0318</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4314268024225672</v>
+        <v>-0.423445995154436</v>
       </c>
       <c r="J6" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="K6" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="L6" t="n">
-        <v>0.09138682427409162</v>
+        <v>0.08946064823897515</v>
       </c>
       <c r="M6" t="n">
-        <v>7.643095096952123</v>
+        <v>7.626967645102637</v>
       </c>
       <c r="N6" t="n">
-        <v>97.73315252232702</v>
+        <v>97.26622690076863</v>
       </c>
       <c r="O6" t="n">
-        <v>9.886007916359718</v>
+        <v>9.862364163869058</v>
       </c>
       <c r="P6" t="n">
-        <v>267.9412658686741</v>
+        <v>267.8563257476268</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -25371,28 +25541,28 @@
         <v>0.039</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3895476518458872</v>
+        <v>-0.3943192793362701</v>
       </c>
       <c r="J7" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="K7" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="L7" t="n">
-        <v>0.09343403701203901</v>
+        <v>0.0968289860354149</v>
       </c>
       <c r="M7" t="n">
-        <v>7.124008446685789</v>
+        <v>7.092461591098623</v>
       </c>
       <c r="N7" t="n">
-        <v>77.75846811086187</v>
+        <v>77.29652331712829</v>
       </c>
       <c r="O7" t="n">
-        <v>8.818076213713617</v>
+        <v>8.791844136307711</v>
       </c>
       <c r="P7" t="n">
-        <v>279.8200407341672</v>
+        <v>279.870834388564</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -25449,28 +25619,28 @@
         <v>0.0536</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3266266602588386</v>
+        <v>-0.3347566993405044</v>
       </c>
       <c r="J8" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="K8" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0658158488208973</v>
+        <v>0.06976503264720424</v>
       </c>
       <c r="M8" t="n">
-        <v>7.41184929950299</v>
+        <v>7.398763711560753</v>
       </c>
       <c r="N8" t="n">
-        <v>79.97191353992655</v>
+        <v>79.63660615411202</v>
       </c>
       <c r="O8" t="n">
-        <v>8.942701691319384</v>
+        <v>8.92393445483056</v>
       </c>
       <c r="P8" t="n">
-        <v>286.9268071762515</v>
+        <v>287.0133426155182</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -25527,28 +25697,28 @@
         <v>0.0876</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.207246816037504</v>
+        <v>-0.2152500385719089</v>
       </c>
       <c r="J9" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="K9" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03067945795732818</v>
+        <v>0.0334364317584277</v>
       </c>
       <c r="M9" t="n">
-        <v>6.913859943479652</v>
+        <v>6.905446904860105</v>
       </c>
       <c r="N9" t="n">
-        <v>71.66839645423038</v>
+        <v>71.38324779674036</v>
       </c>
       <c r="O9" t="n">
-        <v>8.465718897661933</v>
+        <v>8.448860739575506</v>
       </c>
       <c r="P9" t="n">
-        <v>281.6587625747654</v>
+        <v>281.7439376390582</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -25605,28 +25775,28 @@
         <v>0.0806</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1281947079792226</v>
+        <v>-0.1421910249858723</v>
       </c>
       <c r="J10" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="K10" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0147203220378036</v>
+        <v>0.01813402903693406</v>
       </c>
       <c r="M10" t="n">
-        <v>6.223210015776502</v>
+        <v>6.245166911182165</v>
       </c>
       <c r="N10" t="n">
-        <v>58.09177248322237</v>
+        <v>58.34472567429544</v>
       </c>
       <c r="O10" t="n">
-        <v>7.621795883072596</v>
+        <v>7.638371925632807</v>
       </c>
       <c r="P10" t="n">
-        <v>280.9088394097535</v>
+        <v>281.0577772021897</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -25683,28 +25853,28 @@
         <v>0.06370000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>0.03393175021963192</v>
+        <v>0.01834055934466322</v>
       </c>
       <c r="J11" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="K11" t="n">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="L11" t="n">
-        <v>0.001118343100619201</v>
+        <v>0.0003273587144614343</v>
       </c>
       <c r="M11" t="n">
-        <v>5.887017663448364</v>
+        <v>5.913154873969663</v>
       </c>
       <c r="N11" t="n">
-        <v>54.28487780340835</v>
+        <v>54.71880480097362</v>
       </c>
       <c r="O11" t="n">
-        <v>7.367827210474493</v>
+        <v>7.397216016919718</v>
       </c>
       <c r="P11" t="n">
-        <v>281.1769500406837</v>
+        <v>281.343137525427</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -25761,28 +25931,28 @@
         <v>0.0562</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.05515571865400271</v>
+        <v>-0.06967118222327351</v>
       </c>
       <c r="J12" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="K12" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="L12" t="n">
-        <v>0.003701430714222465</v>
+        <v>0.005893265912746859</v>
       </c>
       <c r="M12" t="n">
-        <v>5.343884506965957</v>
+        <v>5.383050793481087</v>
       </c>
       <c r="N12" t="n">
-        <v>43.24473064883362</v>
+        <v>43.6397916772239</v>
       </c>
       <c r="O12" t="n">
-        <v>6.576072585429211</v>
+        <v>6.606042058390478</v>
       </c>
       <c r="P12" t="n">
-        <v>286.5321906351031</v>
+        <v>286.686689215305</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -25839,28 +26009,28 @@
         <v>0.0536</v>
       </c>
       <c r="I13" t="n">
-        <v>0.02018563453647973</v>
+        <v>0.02099131215382045</v>
       </c>
       <c r="J13" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="K13" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0004672352345728159</v>
+        <v>0.0005132085467532965</v>
       </c>
       <c r="M13" t="n">
-        <v>5.398841281785909</v>
+        <v>5.373195130285601</v>
       </c>
       <c r="N13" t="n">
-        <v>46.03397526842386</v>
+        <v>45.73636901640815</v>
       </c>
       <c r="O13" t="n">
-        <v>6.784834210828136</v>
+        <v>6.762866922866969</v>
       </c>
       <c r="P13" t="n">
-        <v>279.3999417200818</v>
+        <v>279.391332889699</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -25917,28 +26087,28 @@
         <v>0.0689</v>
       </c>
       <c r="I14" t="n">
-        <v>0.01864779193771647</v>
+        <v>0.006706152102910359</v>
       </c>
       <c r="J14" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="K14" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="L14" t="n">
-        <v>0.000428342164437101</v>
+        <v>5.568179067294565e-05</v>
       </c>
       <c r="M14" t="n">
-        <v>5.003649320462851</v>
+        <v>5.029116117681576</v>
       </c>
       <c r="N14" t="n">
-        <v>42.85585415408491</v>
+        <v>43.04361649162768</v>
       </c>
       <c r="O14" t="n">
-        <v>6.54643828001799</v>
+        <v>6.5607634076857</v>
       </c>
       <c r="P14" t="n">
-        <v>271.8610476466331</v>
+        <v>271.9881739336187</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -25995,28 +26165,28 @@
         <v>0.0704</v>
       </c>
       <c r="I15" t="n">
-        <v>0.05460358736757498</v>
+        <v>0.0508457440133784</v>
       </c>
       <c r="J15" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="K15" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="L15" t="n">
-        <v>0.003731642758367459</v>
+        <v>0.003285754787603623</v>
       </c>
       <c r="M15" t="n">
-        <v>5.026392525941778</v>
+        <v>5.008092809273498</v>
       </c>
       <c r="N15" t="n">
-        <v>42.03885194157083</v>
+        <v>41.79689881603201</v>
       </c>
       <c r="O15" t="n">
-        <v>6.483737497892002</v>
+        <v>6.465052112398786</v>
       </c>
       <c r="P15" t="n">
-        <v>265.714318711489</v>
+        <v>265.7543011698275</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -26073,28 +26243,28 @@
         <v>0.059</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1091564521617005</v>
+        <v>0.1044928915400022</v>
       </c>
       <c r="J16" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="K16" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="L16" t="n">
-        <v>0.02053314973145404</v>
+        <v>0.0191009915472613</v>
       </c>
       <c r="M16" t="n">
-        <v>4.277671415982685</v>
+        <v>4.270814975517758</v>
       </c>
       <c r="N16" t="n">
-        <v>30.01685657641596</v>
+        <v>29.88417067701609</v>
       </c>
       <c r="O16" t="n">
-        <v>5.47876414681413</v>
+        <v>5.466641626905507</v>
       </c>
       <c r="P16" t="n">
-        <v>259.7797937152601</v>
+        <v>259.8294135403378</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -26151,28 +26321,28 @@
         <v>0.0731</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1256582427685796</v>
+        <v>0.1244789866829897</v>
       </c>
       <c r="J17" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="K17" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="L17" t="n">
-        <v>0.03021513832811518</v>
+        <v>0.03011961952500608</v>
       </c>
       <c r="M17" t="n">
-        <v>4.162878323297392</v>
+        <v>4.141340114865566</v>
       </c>
       <c r="N17" t="n">
-        <v>26.76486128542264</v>
+        <v>26.59255779987149</v>
       </c>
       <c r="O17" t="n">
-        <v>5.17347671159566</v>
+        <v>5.156797242462757</v>
       </c>
       <c r="P17" t="n">
-        <v>254.5255757015586</v>
+        <v>254.5381039793787</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -26229,28 +26399,28 @@
         <v>0.08309999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1206463985403926</v>
+        <v>0.115603684550851</v>
       </c>
       <c r="J18" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="K18" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="L18" t="n">
-        <v>0.02945894016636563</v>
+        <v>0.02743443751920904</v>
       </c>
       <c r="M18" t="n">
-        <v>3.981153416316</v>
+        <v>3.978633778750428</v>
       </c>
       <c r="N18" t="n">
-        <v>25.32548308669848</v>
+        <v>25.25023999546977</v>
       </c>
       <c r="O18" t="n">
-        <v>5.032443053497822</v>
+        <v>5.024961690945491</v>
       </c>
       <c r="P18" t="n">
-        <v>253.2753185114786</v>
+        <v>253.3289566951845</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -26307,28 +26477,28 @@
         <v>0.0756</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1171273523988806</v>
+        <v>0.1178175497479623</v>
       </c>
       <c r="J19" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="K19" t="n">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="L19" t="n">
-        <v>0.02148069335790137</v>
+        <v>0.02207212920172352</v>
       </c>
       <c r="M19" t="n">
-        <v>4.53250974888441</v>
+        <v>4.503985335875876</v>
       </c>
       <c r="N19" t="n">
-        <v>33.11174706753823</v>
+        <v>32.88340071878205</v>
       </c>
       <c r="O19" t="n">
-        <v>5.754280760228704</v>
+        <v>5.734405001286712</v>
       </c>
       <c r="P19" t="n">
-        <v>258.8849691964667</v>
+        <v>258.8776302428382</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -26385,28 +26555,28 @@
         <v>0.0958</v>
       </c>
       <c r="I20" t="n">
-        <v>0.03598296896702607</v>
+        <v>0.03728513266866089</v>
       </c>
       <c r="J20" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="K20" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="L20" t="n">
-        <v>0.002611402484045011</v>
+        <v>0.002847983032701507</v>
       </c>
       <c r="M20" t="n">
-        <v>4.013743547614528</v>
+        <v>3.992167193046747</v>
       </c>
       <c r="N20" t="n">
-        <v>26.11660938148756</v>
+        <v>25.94147647269503</v>
       </c>
       <c r="O20" t="n">
-        <v>5.110441212017565</v>
+        <v>5.093277576639136</v>
       </c>
       <c r="P20" t="n">
-        <v>259.5607026130185</v>
+        <v>259.5468422693352</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -26463,28 +26633,28 @@
         <v>0.06610000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1830959556140564</v>
+        <v>0.1772872342738828</v>
       </c>
       <c r="J21" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="K21" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0656539781041291</v>
+        <v>0.06248422144464971</v>
       </c>
       <c r="M21" t="n">
-        <v>3.775764334739525</v>
+        <v>3.7818260702296</v>
       </c>
       <c r="N21" t="n">
-        <v>25.1962794515335</v>
+        <v>25.13405050207862</v>
       </c>
       <c r="O21" t="n">
-        <v>5.019589570027962</v>
+        <v>5.013387128686415</v>
       </c>
       <c r="P21" t="n">
-        <v>267.8178706756401</v>
+        <v>267.8797017719015</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -26541,28 +26711,28 @@
         <v>0.06279999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>0.284715142058472</v>
+        <v>0.2825563751353226</v>
       </c>
       <c r="J22" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="K22" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="L22" t="n">
-        <v>0.091419186874935</v>
+        <v>0.09145909748749825</v>
       </c>
       <c r="M22" t="n">
-        <v>5.144846477946265</v>
+        <v>5.121480755598891</v>
       </c>
       <c r="N22" t="n">
-        <v>42.54803972236287</v>
+        <v>42.2695013039976</v>
       </c>
       <c r="O22" t="n">
-        <v>6.522885843119046</v>
+        <v>6.501499927247373</v>
       </c>
       <c r="P22" t="n">
-        <v>274.3572963832715</v>
+        <v>274.380278259757</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -26600,7 +26770,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W288"/>
+  <dimension ref="A1:W290"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59911,6 +60081,240 @@
         </is>
       </c>
     </row>
+    <row r="289">
+      <c r="A289" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:11:34+00:00</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>-35.51424445461009,174.47059770739537</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>-35.513920006343575,174.46954708032627</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>-35.51410341235057,174.46839199490537</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>-35.51485482391373,174.46757223645113</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>-35.51542771683172,174.4669282781511</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>-35.515987782303235,174.46626689294737</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>-35.51666966336828,174.4656369476921</t>
+        </is>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>-35.51736595713548,174.4651195229018</t>
+        </is>
+      </c>
+      <c r="J289" t="inlineStr">
+        <is>
+          <t>-35.51798691893306,174.46464261956112</t>
+        </is>
+      </c>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>-35.51863962901375,174.46423672079646</t>
+        </is>
+      </c>
+      <c r="L289" t="inlineStr">
+        <is>
+          <t>-35.51934872660399,174.46382038383805</t>
+        </is>
+      </c>
+      <c r="M289" t="inlineStr">
+        <is>
+          <t>-35.520092318062005,174.46349926660042</t>
+        </is>
+      </c>
+      <c r="N289" t="inlineStr">
+        <is>
+          <t>-35.52073731436921,174.46303994629005</t>
+        </is>
+      </c>
+      <c r="O289" t="inlineStr">
+        <is>
+          <t>-35.52142661383632,174.4626979187383</t>
+        </is>
+      </c>
+      <c r="P289" t="inlineStr">
+        <is>
+          <t>-35.522124502776286,174.46233590653603</t>
+        </is>
+      </c>
+      <c r="Q289" t="inlineStr">
+        <is>
+          <t>-35.52282552320164,174.4620275773919</t>
+        </is>
+      </c>
+      <c r="R289" t="inlineStr">
+        <is>
+          <t>-35.52351305579864,174.46170460763608</t>
+        </is>
+      </c>
+      <c r="S289" t="inlineStr">
+        <is>
+          <t>-35.52432407227258,174.46152525996234</t>
+        </is>
+      </c>
+      <c r="T289" t="inlineStr">
+        <is>
+          <t>-35.52513258714398,174.4613930699129</t>
+        </is>
+      </c>
+      <c r="U289" t="inlineStr">
+        <is>
+          <t>-35.52586638783162,174.46137337365832</t>
+        </is>
+      </c>
+      <c r="V289" t="inlineStr">
+        <is>
+          <t>-35.52660394027093,174.46139743647205</t>
+        </is>
+      </c>
+      <c r="W289" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:11:35+00:00</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>-35.514072721952594,174.47053660480162</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>-35.513920006343575,174.46954708032627</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>-35.51410341235057,174.46839199490537</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>-35.51485482391373,174.46757223645113</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>-35.51542771683172,174.4669282781511</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>-35.51598214593117,174.46625960267676</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>-35.51666588482204,174.4656302235007</t>
+        </is>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>-35.51736729821023,174.46512252171496</t>
+        </is>
+      </c>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>-35.51799747454753,174.46466622327026</t>
+        </is>
+      </c>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>-35.518650400978814,174.46426080835482</t>
+        </is>
+      </c>
+      <c r="L290" t="inlineStr">
+        <is>
+          <t>-35.51934494906123,174.46381037219</t>
+        </is>
+      </c>
+      <c r="M290" t="inlineStr">
+        <is>
+          <t>-35.520102778165175,174.46353333064405</t>
+        </is>
+      </c>
+      <c r="N290" t="inlineStr">
+        <is>
+          <t>-35.52072783568358,174.46300861178278</t>
+        </is>
+      </c>
+      <c r="O290" t="inlineStr">
+        <is>
+          <t>-35.521430230823114,174.46271038925573</t>
+        </is>
+      </c>
+      <c r="P290" t="inlineStr">
+        <is>
+          <t>-35.52212845382191,174.46235080012147</t>
+        </is>
+      </c>
+      <c r="Q290" t="inlineStr">
+        <is>
+          <t>-35.52283138608016,174.46205075237117</t>
+        </is>
+      </c>
+      <c r="R290" t="inlineStr">
+        <is>
+          <t>-35.52352114551849,174.46173698202927</t>
+        </is>
+      </c>
+      <c r="S290" t="inlineStr">
+        <is>
+          <t>-35.52432430478512,174.46152666499185</t>
+        </is>
+      </c>
+      <c r="T290" t="inlineStr">
+        <is>
+          <t>-35.525132721122915,174.46139460500365</t>
+        </is>
+      </c>
+      <c r="U290" t="inlineStr">
+        <is>
+          <t>-35.525865576720186,174.46136405307544</t>
+        </is>
+      </c>
+      <c r="V290" t="inlineStr">
+        <is>
+          <t>-35.526603397915736,174.46139118593794</t>
+        </is>
+      </c>
+      <c r="W290" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0086/nzd0086.xlsx
+++ b/data/nzd0086/nzd0086.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W290"/>
+  <dimension ref="A1:W291"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21964,7 +21964,7 @@
         <v>283.88</v>
       </c>
       <c r="C290" t="n">
-        <v>243.46</v>
+        <v>208.62</v>
       </c>
       <c r="D290" t="n">
         <v>232.44</v>
@@ -21994,7 +21994,7 @@
         <v>274.45</v>
       </c>
       <c r="M290" t="n">
-        <v>282.14</v>
+        <v>272.94</v>
       </c>
       <c r="N290" t="n">
         <v>262.52</v>
@@ -22026,6 +22026,81 @@
       <c r="W290" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:11:04+00:00</t>
+        </is>
+      </c>
+      <c r="B291" t="n">
+        <v>283.88</v>
+      </c>
+      <c r="C291" t="n">
+        <v>208.62</v>
+      </c>
+      <c r="D291" t="n">
+        <v>228.4</v>
+      </c>
+      <c r="E291" t="n">
+        <v>250.12</v>
+      </c>
+      <c r="F291" t="n">
+        <v>258.88</v>
+      </c>
+      <c r="G291" t="n">
+        <v>263.55</v>
+      </c>
+      <c r="H291" t="n">
+        <v>270.97</v>
+      </c>
+      <c r="I291" t="n">
+        <v>268.86</v>
+      </c>
+      <c r="J291" t="n">
+        <v>268.09</v>
+      </c>
+      <c r="K291" t="n">
+        <v>271.15</v>
+      </c>
+      <c r="L291" t="n">
+        <v>274.22</v>
+      </c>
+      <c r="M291" t="n">
+        <v>270.14</v>
+      </c>
+      <c r="N291" t="n">
+        <v>262.43</v>
+      </c>
+      <c r="O291" t="n">
+        <v>262.64</v>
+      </c>
+      <c r="P291" t="n">
+        <v>259.31</v>
+      </c>
+      <c r="Q291" t="n">
+        <v>256.39</v>
+      </c>
+      <c r="R291" t="n">
+        <v>253.69</v>
+      </c>
+      <c r="S291" t="n">
+        <v>258.8</v>
+      </c>
+      <c r="T291" t="n">
+        <v>259.57</v>
+      </c>
+      <c r="U291" t="n">
+        <v>267.6</v>
+      </c>
+      <c r="V291" t="n">
+        <v>278.36</v>
+      </c>
+      <c r="W291" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -22040,7 +22115,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B294"/>
+  <dimension ref="A1:B295"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24983,6 +25058,16 @@
       </c>
       <c r="B294" t="n">
         <v>-0.61</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B295" t="n">
+        <v>0.16</v>
       </c>
     </row>
   </sheetData>
@@ -25151,28 +25236,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6379761021027339</v>
+        <v>0.6173385965523678</v>
       </c>
       <c r="J2" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="K2" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06129141430324059</v>
+        <v>0.05777949021126894</v>
       </c>
       <c r="M2" t="n">
-        <v>13.86637196355964</v>
+        <v>13.89770813082253</v>
       </c>
       <c r="N2" t="n">
-        <v>306.452918277079</v>
+        <v>307.2878666615327</v>
       </c>
       <c r="O2" t="n">
-        <v>17.50579670500829</v>
+        <v>17.52962825223435</v>
       </c>
       <c r="P2" t="n">
-        <v>289.5746099368026</v>
+        <v>289.8064254842363</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -25229,28 +25314,28 @@
         <v>0.0101</v>
       </c>
       <c r="I3" t="n">
-        <v>1.434675182730626</v>
+        <v>1.41128564324707</v>
       </c>
       <c r="J3" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="K3" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07201456017775443</v>
+        <v>0.0708237225858136</v>
       </c>
       <c r="M3" t="n">
-        <v>29.42589409123895</v>
+        <v>29.24269665728508</v>
       </c>
       <c r="N3" t="n">
-        <v>1245.966831011822</v>
+        <v>1234.495708060078</v>
       </c>
       <c r="O3" t="n">
-        <v>35.29825535365484</v>
+        <v>35.13539110441319</v>
       </c>
       <c r="P3" t="n">
-        <v>162.4109759234416</v>
+        <v>162.6782811108836</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -25307,28 +25392,28 @@
         <v>0.0205</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.082610428666785</v>
+        <v>-1.074680419010831</v>
       </c>
       <c r="J4" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="K4" t="n">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="L4" t="n">
-        <v>0.07296617635257363</v>
+        <v>0.07250776692836791</v>
       </c>
       <c r="M4" t="n">
-        <v>19.35272594371768</v>
+        <v>19.31744393789906</v>
       </c>
       <c r="N4" t="n">
-        <v>707.3286154075776</v>
+        <v>705.12117215554</v>
       </c>
       <c r="O4" t="n">
-        <v>26.59565030992056</v>
+        <v>26.55411780036271</v>
       </c>
       <c r="P4" t="n">
-        <v>247.2472833980531</v>
+        <v>247.1554951329923</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -25385,28 +25470,28 @@
         <v>0.0258</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.412044693394206</v>
+        <v>-0.4086177191137579</v>
       </c>
       <c r="J5" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="K5" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06460517023334278</v>
+        <v>0.06404538553959915</v>
       </c>
       <c r="M5" t="n">
-        <v>8.557890939468056</v>
+        <v>8.545108266694402</v>
       </c>
       <c r="N5" t="n">
-        <v>131.0133860739638</v>
+        <v>130.6398784732864</v>
       </c>
       <c r="O5" t="n">
-        <v>11.44610790067802</v>
+        <v>11.4297803335535</v>
       </c>
       <c r="P5" t="n">
-        <v>256.2978776320865</v>
+        <v>256.2612580373524</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -25463,28 +25548,28 @@
         <v>0.0318</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.423445995154436</v>
+        <v>-0.4218064117891804</v>
       </c>
       <c r="J6" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="K6" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08946064823897515</v>
+        <v>0.08946539256440955</v>
       </c>
       <c r="M6" t="n">
-        <v>7.626967645102637</v>
+        <v>7.608406445055691</v>
       </c>
       <c r="N6" t="n">
-        <v>97.26622690076863</v>
+        <v>96.94874042986596</v>
       </c>
       <c r="O6" t="n">
-        <v>9.862364163869058</v>
+        <v>9.846255147509938</v>
       </c>
       <c r="P6" t="n">
-        <v>267.8563257476268</v>
+        <v>267.8388056633033</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -25541,28 +25626,28 @@
         <v>0.039</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3943192793362701</v>
+        <v>-0.3984894938798089</v>
       </c>
       <c r="J7" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="K7" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0968289860354149</v>
+        <v>0.0992642522000855</v>
       </c>
       <c r="M7" t="n">
-        <v>7.092461591098623</v>
+        <v>7.083284956413843</v>
       </c>
       <c r="N7" t="n">
-        <v>77.29652331712829</v>
+        <v>77.14587463540758</v>
       </c>
       <c r="O7" t="n">
-        <v>8.791844136307711</v>
+        <v>8.783272433177032</v>
       </c>
       <c r="P7" t="n">
-        <v>279.870834388564</v>
+        <v>279.9153960204998</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -25619,28 +25704,28 @@
         <v>0.0536</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3347566993405044</v>
+        <v>-0.3398573698936955</v>
       </c>
       <c r="J8" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="K8" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="L8" t="n">
-        <v>0.06976503264720424</v>
+        <v>0.07214212859607727</v>
       </c>
       <c r="M8" t="n">
-        <v>7.398763711560753</v>
+        <v>7.397050772017008</v>
       </c>
       <c r="N8" t="n">
-        <v>79.63660615411202</v>
+        <v>79.53537264188638</v>
       </c>
       <c r="O8" t="n">
-        <v>8.92393445483056</v>
+        <v>8.918260628726118</v>
       </c>
       <c r="P8" t="n">
-        <v>287.0133426155182</v>
+        <v>287.0678468146293</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -25697,28 +25782,28 @@
         <v>0.0876</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2152500385719089</v>
+        <v>-0.2203656542360581</v>
       </c>
       <c r="J9" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="K9" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0334364317584277</v>
+        <v>0.0351763415669295</v>
       </c>
       <c r="M9" t="n">
-        <v>6.905446904860105</v>
+        <v>6.906781598701948</v>
       </c>
       <c r="N9" t="n">
-        <v>71.38324779674036</v>
+        <v>71.31149161958183</v>
       </c>
       <c r="O9" t="n">
-        <v>8.448860739575506</v>
+        <v>8.444613171696014</v>
       </c>
       <c r="P9" t="n">
-        <v>281.7439376390582</v>
+        <v>281.7986015370353</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -25775,28 +25860,28 @@
         <v>0.0806</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1421910249858723</v>
+        <v>-0.1487583793460933</v>
       </c>
       <c r="J10" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="K10" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01813402903693406</v>
+        <v>0.01987359401609656</v>
       </c>
       <c r="M10" t="n">
-        <v>6.245166911182165</v>
+        <v>6.253912934675073</v>
       </c>
       <c r="N10" t="n">
-        <v>58.34472567429544</v>
+        <v>58.43095500018784</v>
       </c>
       <c r="O10" t="n">
-        <v>7.638371925632807</v>
+        <v>7.644014324959618</v>
       </c>
       <c r="P10" t="n">
-        <v>281.0577772021897</v>
+        <v>281.1279539340427</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -25853,28 +25938,28 @@
         <v>0.06370000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>0.01834055934466322</v>
+        <v>0.01068807056355823</v>
       </c>
       <c r="J11" t="n">
+        <v>290</v>
+      </c>
+      <c r="K11" t="n">
         <v>289</v>
       </c>
-      <c r="K11" t="n">
-        <v>288</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.0003273587144614343</v>
+        <v>0.0001112923197746918</v>
       </c>
       <c r="M11" t="n">
-        <v>5.913154873969663</v>
+        <v>5.925768594773255</v>
       </c>
       <c r="N11" t="n">
-        <v>54.71880480097362</v>
+        <v>54.9198589065455</v>
       </c>
       <c r="O11" t="n">
-        <v>7.397216016919718</v>
+        <v>7.410793406008934</v>
       </c>
       <c r="P11" t="n">
-        <v>281.343137525427</v>
+        <v>281.4250465649393</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -25931,28 +26016,28 @@
         <v>0.0562</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.06967118222327351</v>
+        <v>-0.07726284621741225</v>
       </c>
       <c r="J12" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="K12" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="L12" t="n">
-        <v>0.005893265912746859</v>
+        <v>0.007232068254915847</v>
       </c>
       <c r="M12" t="n">
-        <v>5.383050793481087</v>
+        <v>5.403836530141795</v>
       </c>
       <c r="N12" t="n">
-        <v>43.6397916772239</v>
+        <v>43.87337670597002</v>
       </c>
       <c r="O12" t="n">
-        <v>6.606042058390478</v>
+        <v>6.623698114042489</v>
       </c>
       <c r="P12" t="n">
-        <v>286.686689215305</v>
+        <v>286.7678114053397</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -26009,28 +26094,28 @@
         <v>0.0536</v>
       </c>
       <c r="I13" t="n">
-        <v>0.02099131215382045</v>
+        <v>0.007429684104012548</v>
       </c>
       <c r="J13" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="K13" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0005132085467532965</v>
+        <v>6.417481073528464e-05</v>
       </c>
       <c r="M13" t="n">
-        <v>5.373195130285601</v>
+        <v>5.398042993573356</v>
       </c>
       <c r="N13" t="n">
-        <v>45.73636901640815</v>
+        <v>46.04926059090712</v>
       </c>
       <c r="O13" t="n">
-        <v>6.762866922866969</v>
+        <v>6.785960550350048</v>
       </c>
       <c r="P13" t="n">
-        <v>279.391332889699</v>
+        <v>279.536060522798</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -26087,28 +26172,28 @@
         <v>0.0689</v>
       </c>
       <c r="I14" t="n">
-        <v>0.006706152102910359</v>
+        <v>-0.0002589914324467904</v>
       </c>
       <c r="J14" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="K14" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="L14" t="n">
-        <v>5.568179067294565e-05</v>
+        <v>8.309515298066117e-08</v>
       </c>
       <c r="M14" t="n">
-        <v>5.029116117681576</v>
+        <v>5.046980693445524</v>
       </c>
       <c r="N14" t="n">
-        <v>43.04361649162768</v>
+        <v>43.21848096119232</v>
       </c>
       <c r="O14" t="n">
-        <v>6.5607634076857</v>
+        <v>6.574076434085043</v>
       </c>
       <c r="P14" t="n">
-        <v>271.9881739336187</v>
+        <v>272.0626013184358</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -26165,28 +26250,28 @@
         <v>0.0704</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0508457440133784</v>
+        <v>0.04764932347397997</v>
       </c>
       <c r="J15" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="K15" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="L15" t="n">
-        <v>0.003285754787603623</v>
+        <v>0.002905167273682174</v>
       </c>
       <c r="M15" t="n">
-        <v>5.008092809273498</v>
+        <v>5.004649992885501</v>
       </c>
       <c r="N15" t="n">
-        <v>41.79689881603201</v>
+        <v>41.72085806786158</v>
       </c>
       <c r="O15" t="n">
-        <v>6.465052112398786</v>
+        <v>6.459168527594057</v>
       </c>
       <c r="P15" t="n">
-        <v>265.7543011698275</v>
+        <v>265.7884571380879</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -26243,28 +26328,28 @@
         <v>0.059</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1044928915400022</v>
+        <v>0.1021301220928835</v>
       </c>
       <c r="J16" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="K16" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0191009915472613</v>
+        <v>0.0183840213041595</v>
       </c>
       <c r="M16" t="n">
-        <v>4.270814975517758</v>
+        <v>4.267626962438047</v>
       </c>
       <c r="N16" t="n">
-        <v>29.88417067701609</v>
+        <v>29.81832462805987</v>
       </c>
       <c r="O16" t="n">
-        <v>5.466641626905507</v>
+        <v>5.460615773707199</v>
       </c>
       <c r="P16" t="n">
-        <v>259.8294135403378</v>
+        <v>259.8546613690412</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -26321,28 +26406,28 @@
         <v>0.0731</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1244789866829897</v>
+        <v>0.123437804250087</v>
       </c>
       <c r="J17" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="K17" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="L17" t="n">
-        <v>0.03011961952500608</v>
+        <v>0.02985580377241004</v>
       </c>
       <c r="M17" t="n">
-        <v>4.141340114865566</v>
+        <v>4.131749913032953</v>
       </c>
       <c r="N17" t="n">
-        <v>26.59255779987149</v>
+        <v>26.50808347509951</v>
       </c>
       <c r="O17" t="n">
-        <v>5.156797242462757</v>
+        <v>5.148600147137036</v>
       </c>
       <c r="P17" t="n">
-        <v>254.5381039793787</v>
+        <v>254.5492297351088</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -26399,28 +26484,28 @@
         <v>0.08309999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>0.115603684550851</v>
+        <v>0.1136615505451027</v>
       </c>
       <c r="J18" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="K18" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="L18" t="n">
-        <v>0.02743443751920904</v>
+        <v>0.02672622655596024</v>
       </c>
       <c r="M18" t="n">
-        <v>3.978633778750428</v>
+        <v>3.974419469169735</v>
       </c>
       <c r="N18" t="n">
-        <v>25.25023999546977</v>
+        <v>25.18830593224127</v>
       </c>
       <c r="O18" t="n">
-        <v>5.024961690945491</v>
+        <v>5.018795267017899</v>
       </c>
       <c r="P18" t="n">
-        <v>253.3289566951845</v>
+        <v>253.3497097427388</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -26477,28 +26562,28 @@
         <v>0.0756</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1178175497479623</v>
+        <v>0.1155215561349299</v>
       </c>
       <c r="J19" t="n">
+        <v>290</v>
+      </c>
+      <c r="K19" t="n">
         <v>289</v>
       </c>
-      <c r="K19" t="n">
-        <v>288</v>
-      </c>
       <c r="L19" t="n">
-        <v>0.02207212920172352</v>
+        <v>0.02138262296494775</v>
       </c>
       <c r="M19" t="n">
-        <v>4.503985335875876</v>
+        <v>4.500726296287491</v>
       </c>
       <c r="N19" t="n">
-        <v>32.88340071878205</v>
+        <v>32.80489422390905</v>
       </c>
       <c r="O19" t="n">
-        <v>5.734405001286712</v>
+        <v>5.727555693654061</v>
       </c>
       <c r="P19" t="n">
-        <v>258.8776302428382</v>
+        <v>258.9021381677505</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -26555,28 +26640,28 @@
         <v>0.0958</v>
       </c>
       <c r="I20" t="n">
-        <v>0.03728513266866089</v>
+        <v>0.03658963839773691</v>
       </c>
       <c r="J20" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="K20" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="L20" t="n">
-        <v>0.002847983032701507</v>
+        <v>0.002764646763485645</v>
       </c>
       <c r="M20" t="n">
-        <v>3.992167193046747</v>
+        <v>3.981759018281466</v>
       </c>
       <c r="N20" t="n">
-        <v>25.94147647269503</v>
+        <v>25.85524655028317</v>
       </c>
       <c r="O20" t="n">
-        <v>5.093277576639136</v>
+        <v>5.084805458450026</v>
       </c>
       <c r="P20" t="n">
-        <v>259.5468422693352</v>
+        <v>259.5542741075274</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -26633,28 +26718,28 @@
         <v>0.06610000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1772872342738828</v>
+        <v>0.1737115620566403</v>
       </c>
       <c r="J21" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="K21" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="L21" t="n">
-        <v>0.06248422144464971</v>
+        <v>0.06040010780962768</v>
       </c>
       <c r="M21" t="n">
-        <v>3.7818260702296</v>
+        <v>3.788564989198203</v>
       </c>
       <c r="N21" t="n">
-        <v>25.13405050207862</v>
+        <v>25.13258311244491</v>
       </c>
       <c r="O21" t="n">
-        <v>5.013387128686415</v>
+        <v>5.013240779420524</v>
       </c>
       <c r="P21" t="n">
-        <v>267.8797017719015</v>
+        <v>267.9179103071228</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -26711,28 +26796,28 @@
         <v>0.06279999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2825563751353226</v>
+        <v>0.2800211342052046</v>
       </c>
       <c r="J22" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="K22" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="L22" t="n">
-        <v>0.09145909748749825</v>
+        <v>0.09054584376139929</v>
       </c>
       <c r="M22" t="n">
-        <v>5.121480755598891</v>
+        <v>5.118052405580298</v>
       </c>
       <c r="N22" t="n">
-        <v>42.2695013039976</v>
+        <v>42.16657672215796</v>
       </c>
       <c r="O22" t="n">
-        <v>6.501499927247373</v>
+        <v>6.493579653947271</v>
       </c>
       <c r="P22" t="n">
-        <v>274.380278259757</v>
+        <v>274.4073690657616</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -26770,7 +26855,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W290"/>
+  <dimension ref="A1:W291"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60211,7 +60296,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>-35.513920006343575,174.46954708032627</t>
+          <t>-35.513618434672665,174.4694397846393</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -60261,7 +60346,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>-35.520102778165175,174.46353333064405</t>
+          <t>-35.5200736166409,174.4634383642407</t>
         </is>
       </c>
       <c r="N290" t="inlineStr">
@@ -60312,6 +60397,123 @@
       <c r="W290" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:11:04+00:00</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>-35.514072721952594,174.47053660480162</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>-35.513618434672665,174.4694397846393</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>-35.51407102748622,174.46837161698556</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>-35.514820490783706,174.46753567243977</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>-35.51540689964894,174.4669040124579</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>-35.51596876728791,174.46624229830223</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>-35.516659451080244,174.4656187742033</t>
+        </is>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>-35.51735916523965,174.46510433536582</t>
+        </is>
+      </c>
+      <c r="J291" t="inlineStr">
+        <is>
+          <t>-35.517993667605154,174.4646577104564</t>
+        </is>
+      </c>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>-35.51864473380103,174.46424813578318</t>
+        </is>
+      </c>
+      <c r="L291" t="inlineStr">
+        <is>
+          <t>-35.519344080226276,174.4638080695111</t>
+        </is>
+      </c>
+      <c r="M291" t="inlineStr">
+        <is>
+          <t>-35.520064741379194,174.46340946143545</t>
+        </is>
+      </c>
+      <c r="N291" t="inlineStr">
+        <is>
+          <t>-35.52072755413834,174.46300768105493</t>
+        </is>
+      </c>
+      <c r="O291" t="inlineStr">
+        <is>
+          <t>-35.52142269543248,174.46268440901227</t>
+        </is>
+      </c>
+      <c r="P291" t="inlineStr">
+        <is>
+          <t>-35.522126172232404,174.46234219960013</t>
+        </is>
+      </c>
+      <c r="Q291" t="inlineStr">
+        <is>
+          <t>-35.522826749076614,174.46203242306913</t>
+        </is>
+      </c>
+      <c r="R291" t="inlineStr">
+        <is>
+          <t>-35.52351903744902,174.46172854570472</t>
+        </is>
+      </c>
+      <c r="S291" t="inlineStr">
+        <is>
+          <t>-35.52431761557171,174.461486243377</t>
+        </is>
+      </c>
+      <c r="T291" t="inlineStr">
+        <is>
+          <t>-35.525130883695745,174.46137355233074</t>
+        </is>
+      </c>
+      <c r="U291" t="inlineStr">
+        <is>
+          <t>-35.52586500417049,174.46135747384054</t>
+        </is>
+      </c>
+      <c r="V291" t="inlineStr">
+        <is>
+          <t>-35.526601723273046,174.46137188604357</t>
+        </is>
+      </c>
+      <c r="W291" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>

--- a/data/nzd0086/nzd0086.xlsx
+++ b/data/nzd0086/nzd0086.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W291"/>
+  <dimension ref="A1:W292"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21964,7 +21964,7 @@
         <v>283.88</v>
       </c>
       <c r="C290" t="n">
-        <v>208.62</v>
+        <v>243.46</v>
       </c>
       <c r="D290" t="n">
         <v>232.44</v>
@@ -22039,7 +22039,7 @@
         <v>283.88</v>
       </c>
       <c r="C291" t="n">
-        <v>208.62</v>
+        <v>243.46</v>
       </c>
       <c r="D291" t="n">
         <v>228.4</v>
@@ -22099,6 +22099,81 @@
         <v>278.36</v>
       </c>
       <c r="W291" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B292" t="n">
+        <v>264.04</v>
+      </c>
+      <c r="C292" t="n">
+        <v>240.28</v>
+      </c>
+      <c r="D292" t="n">
+        <v>227.75</v>
+      </c>
+      <c r="E292" t="n">
+        <v>243.61</v>
+      </c>
+      <c r="F292" t="n">
+        <v>254.88</v>
+      </c>
+      <c r="G292" t="n">
+        <v>259.99</v>
+      </c>
+      <c r="H292" t="n">
+        <v>268.96</v>
+      </c>
+      <c r="I292" t="n">
+        <v>266.88</v>
+      </c>
+      <c r="J292" t="n">
+        <v>265.9</v>
+      </c>
+      <c r="K292" t="n">
+        <v>267.95</v>
+      </c>
+      <c r="L292" t="n">
+        <v>269.5</v>
+      </c>
+      <c r="M292" t="n">
+        <v>264.18</v>
+      </c>
+      <c r="N292" t="n">
+        <v>259.47</v>
+      </c>
+      <c r="O292" t="n">
+        <v>259.46</v>
+      </c>
+      <c r="P292" t="n">
+        <v>256.03</v>
+      </c>
+      <c r="Q292" t="n">
+        <v>254.85</v>
+      </c>
+      <c r="R292" t="n">
+        <v>253.87</v>
+      </c>
+      <c r="S292" t="n">
+        <v>257.56</v>
+      </c>
+      <c r="T292" t="n">
+        <v>258.25</v>
+      </c>
+      <c r="U292" t="n">
+        <v>266.96</v>
+      </c>
+      <c r="V292" t="n">
+        <v>276.39</v>
+      </c>
+      <c r="W292" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -22115,7 +22190,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B295"/>
+  <dimension ref="A1:B296"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25068,6 +25143,16 @@
       </c>
       <c r="B295" t="n">
         <v>0.16</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B296" t="n">
+        <v>-0.46</v>
       </c>
     </row>
   </sheetData>
@@ -25236,28 +25321,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6173385965523678</v>
+        <v>0.5791107670323344</v>
       </c>
       <c r="J2" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="K2" t="n">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05777949021126894</v>
+        <v>0.0505395946553534</v>
       </c>
       <c r="M2" t="n">
-        <v>13.89770813082253</v>
+        <v>14.0029519231916</v>
       </c>
       <c r="N2" t="n">
-        <v>307.2878666615327</v>
+        <v>313.3159798939792</v>
       </c>
       <c r="O2" t="n">
-        <v>17.52962825223435</v>
+        <v>17.70073388009602</v>
       </c>
       <c r="P2" t="n">
-        <v>289.8064254842363</v>
+        <v>290.2372362972626</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -25314,28 +25399,28 @@
         <v>0.0101</v>
       </c>
       <c r="I3" t="n">
-        <v>1.41128564324707</v>
+        <v>1.506454002746823</v>
       </c>
       <c r="J3" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="K3" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0708237225858136</v>
+        <v>0.07946069096718211</v>
       </c>
       <c r="M3" t="n">
-        <v>29.24269665728508</v>
+        <v>29.41031740314746</v>
       </c>
       <c r="N3" t="n">
-        <v>1234.495708060078</v>
+        <v>1249.126009377804</v>
       </c>
       <c r="O3" t="n">
-        <v>35.13539110441319</v>
+        <v>35.34297680413754</v>
       </c>
       <c r="P3" t="n">
-        <v>162.6782811108836</v>
+        <v>161.5869262421367</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -25392,28 +25477,28 @@
         <v>0.0205</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.074680419010831</v>
+        <v>-1.067311189241451</v>
       </c>
       <c r="J4" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="K4" t="n">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="L4" t="n">
-        <v>0.07250776692836791</v>
+        <v>0.07211998577384615</v>
       </c>
       <c r="M4" t="n">
-        <v>19.31744393789906</v>
+        <v>19.28024673879371</v>
       </c>
       <c r="N4" t="n">
-        <v>705.12117215554</v>
+        <v>702.8836439728008</v>
       </c>
       <c r="O4" t="n">
-        <v>26.55411780036271</v>
+        <v>26.51195285098404</v>
       </c>
       <c r="P4" t="n">
-        <v>247.1554951329923</v>
+        <v>247.0699198060713</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -25470,28 +25555,28 @@
         <v>0.0258</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4086177191137579</v>
+        <v>-0.4098605106958924</v>
       </c>
       <c r="J5" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="K5" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06404538553959915</v>
+        <v>0.0648899122473181</v>
       </c>
       <c r="M5" t="n">
-        <v>8.545108266694402</v>
+        <v>8.521588425382081</v>
       </c>
       <c r="N5" t="n">
-        <v>130.6398784732864</v>
+        <v>130.2012755435788</v>
       </c>
       <c r="O5" t="n">
-        <v>11.4297803335535</v>
+        <v>11.41057735364775</v>
       </c>
       <c r="P5" t="n">
-        <v>256.2612580373524</v>
+        <v>256.2745850274503</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -25548,28 +25633,28 @@
         <v>0.0318</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4218064117891804</v>
+        <v>-0.4230120847287869</v>
       </c>
       <c r="J6" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="K6" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08946539256440955</v>
+        <v>0.09058083048597754</v>
       </c>
       <c r="M6" t="n">
-        <v>7.608406445055691</v>
+        <v>7.58809225110075</v>
       </c>
       <c r="N6" t="n">
-        <v>96.94874042986596</v>
+        <v>96.62530668630134</v>
       </c>
       <c r="O6" t="n">
-        <v>9.846255147509938</v>
+        <v>9.829817225477864</v>
       </c>
       <c r="P6" t="n">
-        <v>267.8388056633033</v>
+        <v>267.8517346141896</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -25626,28 +25711,28 @@
         <v>0.039</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3984894938798089</v>
+        <v>-0.4051072586752561</v>
       </c>
       <c r="J7" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="K7" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0992642522000855</v>
+        <v>0.1026353882426336</v>
       </c>
       <c r="M7" t="n">
-        <v>7.083284956413843</v>
+        <v>7.082840902934774</v>
       </c>
       <c r="N7" t="n">
-        <v>77.14587463540758</v>
+        <v>77.17371183641241</v>
       </c>
       <c r="O7" t="n">
-        <v>8.783272433177032</v>
+        <v>8.78485696163645</v>
       </c>
       <c r="P7" t="n">
-        <v>279.9153960204998</v>
+        <v>279.9863611663591</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -25704,28 +25789,28 @@
         <v>0.0536</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3398573698936955</v>
+        <v>-0.3462940463570596</v>
       </c>
       <c r="J8" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="K8" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="L8" t="n">
-        <v>0.07214212859607727</v>
+        <v>0.07500749367200155</v>
       </c>
       <c r="M8" t="n">
-        <v>7.397050772017008</v>
+        <v>7.401284933758989</v>
       </c>
       <c r="N8" t="n">
-        <v>79.53537264188638</v>
+        <v>79.53918567704336</v>
       </c>
       <c r="O8" t="n">
-        <v>8.918260628726118</v>
+        <v>8.918474403004325</v>
       </c>
       <c r="P8" t="n">
-        <v>287.0678468146293</v>
+        <v>287.1368700722081</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -25782,28 +25867,28 @@
         <v>0.0876</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2203656542360581</v>
+        <v>-0.2268031333611308</v>
       </c>
       <c r="J9" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="K9" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0351763415669295</v>
+        <v>0.0373316423977833</v>
       </c>
       <c r="M9" t="n">
-        <v>6.906781598701948</v>
+        <v>6.914816518678069</v>
       </c>
       <c r="N9" t="n">
-        <v>71.31149161958183</v>
+        <v>71.34363453561565</v>
       </c>
       <c r="O9" t="n">
-        <v>8.444613171696014</v>
+        <v>8.44651611823571</v>
       </c>
       <c r="P9" t="n">
-        <v>281.7986015370353</v>
+        <v>281.8676334019017</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -25860,28 +25945,28 @@
         <v>0.0806</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1487583793460933</v>
+        <v>-0.1567831329385715</v>
       </c>
       <c r="J10" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="K10" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01987359401609656</v>
+        <v>0.02204083926655476</v>
       </c>
       <c r="M10" t="n">
-        <v>6.253912934675073</v>
+        <v>6.268993803798376</v>
       </c>
       <c r="N10" t="n">
-        <v>58.43095500018784</v>
+        <v>58.66091038720292</v>
       </c>
       <c r="O10" t="n">
-        <v>7.644014324959618</v>
+        <v>7.659041087969363</v>
       </c>
       <c r="P10" t="n">
-        <v>281.1279539340427</v>
+        <v>281.2140068275464</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -25938,28 +26023,28 @@
         <v>0.06370000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>0.01068807056355823</v>
+        <v>0.000869110613306948</v>
       </c>
       <c r="J11" t="n">
+        <v>291</v>
+      </c>
+      <c r="K11" t="n">
         <v>290</v>
       </c>
-      <c r="K11" t="n">
-        <v>289</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.0001112923197746918</v>
+        <v>7.33247473960752e-07</v>
       </c>
       <c r="M11" t="n">
-        <v>5.925768594773255</v>
+        <v>5.947239075068468</v>
       </c>
       <c r="N11" t="n">
-        <v>54.9198589065455</v>
+        <v>55.3755952073593</v>
       </c>
       <c r="O11" t="n">
-        <v>7.410793406008934</v>
+        <v>7.441478025725757</v>
       </c>
       <c r="P11" t="n">
-        <v>281.4250465649393</v>
+        <v>281.5305167707471</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -26016,28 +26101,28 @@
         <v>0.0562</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.07726284621741225</v>
+        <v>-0.08810032019685285</v>
       </c>
       <c r="J12" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="K12" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="L12" t="n">
-        <v>0.007232068254915847</v>
+        <v>0.009292181827192492</v>
       </c>
       <c r="M12" t="n">
-        <v>5.403836530141795</v>
+        <v>5.440809103954679</v>
       </c>
       <c r="N12" t="n">
-        <v>43.87337670597002</v>
+        <v>44.50823726105301</v>
       </c>
       <c r="O12" t="n">
-        <v>6.623698114042489</v>
+        <v>6.671449412313115</v>
       </c>
       <c r="P12" t="n">
-        <v>286.7678114053397</v>
+        <v>286.8840263125584</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -26094,28 +26179,28 @@
         <v>0.0536</v>
       </c>
       <c r="I13" t="n">
-        <v>0.007429684104012548</v>
+        <v>-0.003654015601963117</v>
       </c>
       <c r="J13" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="K13" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="L13" t="n">
-        <v>6.417481073528464e-05</v>
+        <v>1.537291516862105e-05</v>
       </c>
       <c r="M13" t="n">
-        <v>5.398042993573356</v>
+        <v>5.426872935652275</v>
       </c>
       <c r="N13" t="n">
-        <v>46.04926059090712</v>
+        <v>46.71274811650642</v>
       </c>
       <c r="O13" t="n">
-        <v>6.785960550350048</v>
+        <v>6.834672495189979</v>
       </c>
       <c r="P13" t="n">
-        <v>279.536060522798</v>
+        <v>279.654915814669</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -26172,28 +26257,28 @@
         <v>0.0689</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.0002589914324467904</v>
+        <v>-0.009231242544386217</v>
       </c>
       <c r="J14" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="K14" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="L14" t="n">
-        <v>8.309515298066117e-08</v>
+        <v>0.0001050900730578119</v>
       </c>
       <c r="M14" t="n">
-        <v>5.046980693445524</v>
+        <v>5.074941387223175</v>
       </c>
       <c r="N14" t="n">
-        <v>43.21848096119232</v>
+        <v>43.60843662301344</v>
       </c>
       <c r="O14" t="n">
-        <v>6.574076434085043</v>
+        <v>6.603668421643643</v>
       </c>
       <c r="P14" t="n">
-        <v>272.0626013184358</v>
+        <v>272.1588146364558</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -26250,28 +26335,28 @@
         <v>0.0704</v>
       </c>
       <c r="I15" t="n">
-        <v>0.04764932347397997</v>
+        <v>0.04223115232028789</v>
       </c>
       <c r="J15" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="K15" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="L15" t="n">
-        <v>0.002905167273682174</v>
+        <v>0.002290987659683497</v>
       </c>
       <c r="M15" t="n">
-        <v>5.004649992885501</v>
+        <v>5.010745286679081</v>
       </c>
       <c r="N15" t="n">
-        <v>41.72085806786158</v>
+        <v>41.7738534483978</v>
       </c>
       <c r="O15" t="n">
-        <v>6.459168527594057</v>
+        <v>6.463269563340044</v>
       </c>
       <c r="P15" t="n">
-        <v>265.7884571380879</v>
+        <v>265.8465585239935</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -26328,28 +26413,28 @@
         <v>0.059</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1021301220928835</v>
+        <v>0.09746252056912023</v>
       </c>
       <c r="J16" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="K16" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0183840213041595</v>
+        <v>0.01682102744419567</v>
       </c>
       <c r="M16" t="n">
-        <v>4.267626962438047</v>
+        <v>4.275512524506762</v>
       </c>
       <c r="N16" t="n">
-        <v>29.81832462805987</v>
+        <v>29.86158598887324</v>
       </c>
       <c r="O16" t="n">
-        <v>5.460615773707199</v>
+        <v>5.464575554320138</v>
       </c>
       <c r="P16" t="n">
-        <v>259.8546613690412</v>
+        <v>259.9047140731166</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -26406,28 +26491,28 @@
         <v>0.0731</v>
       </c>
       <c r="I17" t="n">
-        <v>0.123437804250087</v>
+        <v>0.1213019704731647</v>
       </c>
       <c r="J17" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="K17" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="L17" t="n">
-        <v>0.02985580377241004</v>
+        <v>0.02905385007612415</v>
       </c>
       <c r="M17" t="n">
-        <v>4.131749913032953</v>
+        <v>4.127179055344201</v>
       </c>
       <c r="N17" t="n">
-        <v>26.50808347509951</v>
+        <v>26.4475041709193</v>
       </c>
       <c r="O17" t="n">
-        <v>5.148600147137036</v>
+        <v>5.142713697156327</v>
       </c>
       <c r="P17" t="n">
-        <v>254.5492297351088</v>
+        <v>254.5721332017921</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -26484,28 +26569,28 @@
         <v>0.08309999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1136615505451027</v>
+        <v>0.1118696079048301</v>
       </c>
       <c r="J18" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="K18" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="L18" t="n">
-        <v>0.02672622655596024</v>
+        <v>0.02609298909019098</v>
       </c>
       <c r="M18" t="n">
-        <v>3.974419469169735</v>
+        <v>3.969429083992396</v>
       </c>
       <c r="N18" t="n">
-        <v>25.18830593224127</v>
+        <v>25.12322693573208</v>
       </c>
       <c r="O18" t="n">
-        <v>5.018795267017899</v>
+        <v>5.012307546004344</v>
       </c>
       <c r="P18" t="n">
-        <v>253.3497097427388</v>
+        <v>253.3689255164584</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -26562,28 +26647,28 @@
         <v>0.0756</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1155215561349299</v>
+        <v>0.1123680807826851</v>
       </c>
       <c r="J19" t="n">
+        <v>291</v>
+      </c>
+      <c r="K19" t="n">
         <v>290</v>
       </c>
-      <c r="K19" t="n">
-        <v>289</v>
-      </c>
       <c r="L19" t="n">
-        <v>0.02138262296494775</v>
+        <v>0.02037308629734802</v>
       </c>
       <c r="M19" t="n">
-        <v>4.500726296287491</v>
+        <v>4.502126674926357</v>
       </c>
       <c r="N19" t="n">
-        <v>32.80489422390905</v>
+        <v>32.75856979564676</v>
       </c>
       <c r="O19" t="n">
-        <v>5.727555693654061</v>
+        <v>5.723510268676624</v>
       </c>
       <c r="P19" t="n">
-        <v>258.9021381677505</v>
+        <v>258.9359185722986</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -26640,28 +26725,28 @@
         <v>0.0958</v>
       </c>
       <c r="I20" t="n">
-        <v>0.03658963839773691</v>
+        <v>0.03496675368657481</v>
       </c>
       <c r="J20" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="K20" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="L20" t="n">
-        <v>0.002764646763485645</v>
+        <v>0.002543966514449769</v>
       </c>
       <c r="M20" t="n">
-        <v>3.981759018281466</v>
+        <v>3.975822652176479</v>
       </c>
       <c r="N20" t="n">
-        <v>25.85524655028317</v>
+        <v>25.78401408007855</v>
       </c>
       <c r="O20" t="n">
-        <v>5.084805458450026</v>
+        <v>5.077796183392806</v>
       </c>
       <c r="P20" t="n">
-        <v>259.5542741075274</v>
+        <v>259.5716770001657</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -26718,28 +26803,28 @@
         <v>0.06610000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1737115620566403</v>
+        <v>0.169726382373856</v>
       </c>
       <c r="J21" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="K21" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="L21" t="n">
-        <v>0.06040010780962768</v>
+        <v>0.0580250234713624</v>
       </c>
       <c r="M21" t="n">
-        <v>3.788564989198203</v>
+        <v>3.797647974125897</v>
       </c>
       <c r="N21" t="n">
-        <v>25.13258311244491</v>
+        <v>25.15244918269658</v>
       </c>
       <c r="O21" t="n">
-        <v>5.013240779420524</v>
+        <v>5.015221748108112</v>
       </c>
       <c r="P21" t="n">
-        <v>267.9179103071228</v>
+        <v>267.9606451074983</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -26796,28 +26881,28 @@
         <v>0.06279999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2800211342052046</v>
+        <v>0.2761030354226626</v>
       </c>
       <c r="J22" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="K22" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="L22" t="n">
-        <v>0.09054584376139929</v>
+        <v>0.08870080443007777</v>
       </c>
       <c r="M22" t="n">
-        <v>5.118052405580298</v>
+        <v>5.122259876765049</v>
       </c>
       <c r="N22" t="n">
-        <v>42.16657672215796</v>
+        <v>42.12436050042217</v>
       </c>
       <c r="O22" t="n">
-        <v>6.493579653947271</v>
+        <v>6.490328227479884</v>
       </c>
       <c r="P22" t="n">
-        <v>274.4073690657616</v>
+        <v>274.4493845287145</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -26855,7 +26940,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W291"/>
+  <dimension ref="A1:W292"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60296,7 +60381,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>-35.513618434672665,174.4694397846393</t>
+          <t>-35.513920006343575,174.46954708032627</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -60413,7 +60498,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>-35.513618434672665,174.4694397846393</t>
+          <t>-35.513920006343575,174.46954708032627</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -60512,6 +60597,123 @@
         </is>
       </c>
       <c r="W291" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>-35.513900989253116,174.47047550248027</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>-35.513892480576466,174.46953728694228</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>-35.514065817049755,174.4683683383614</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>-35.51477623162211,174.46748853749307</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>-35.51538079659101,174.46687358527407</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>-35.51594671729599,174.46621377814193</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>-35.51664918772788,174.46560050985167</t>
+        </is>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>-35.51735059966118,174.46508518166155</t>
+        </is>
+      </c>
+      <c r="J292" t="inlineStr">
+        <is>
+          <t>-35.51798419350725,174.46463652516178</t>
+        </is>
+      </c>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>-35.51863089030751,174.4642171798903</t>
+        </is>
+      </c>
+      <c r="L292" t="inlineStr">
+        <is>
+          <t>-35.519326250211996,174.4637608145456</t>
+        </is>
+      </c>
+      <c r="M292" t="inlineStr">
+        <is>
+          <t>-35.52004584972706,174.4633479397705</t>
+        </is>
+      </c>
+      <c r="N292" t="inlineStr">
+        <is>
+          <t>-35.52071829442397,174.46297707045426</t>
+        </is>
+      </c>
+      <c r="O292" t="inlineStr">
+        <is>
+          <t>-35.521413110407316,174.46265136214933</t>
+        </is>
+      </c>
+      <c r="P292" t="inlineStr">
+        <is>
+          <t>-35.52211704586818,174.4623077975194</t>
+        </is>
+      </c>
+      <c r="Q292" t="inlineStr">
+        <is>
+          <t>-35.5228226450596,174.46201620058505</t>
+        </is>
+      </c>
+      <c r="R292" t="inlineStr">
+        <is>
+          <t>-35.523519511764704,174.4617304438777</t>
+        </is>
+      </c>
+      <c r="S292" t="inlineStr">
+        <is>
+          <t>-35.52431539775461,174.46147284155956</t>
+        </is>
+      </c>
+      <c r="T292" t="inlineStr">
+        <is>
+          <t>-35.52512962046243,174.4613590786186</t>
+        </is>
+      </c>
+      <c r="U292" t="inlineStr">
+        <is>
+          <t>-35.52586439345043,174.46135045599004</t>
+        </is>
+      </c>
+      <c r="V292" t="inlineStr">
+        <is>
+          <t>-35.52659984881134,174.46135028332174</t>
+        </is>
+      </c>
+      <c r="W292" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
